--- a/lottopy_site/lottopy/lottopy_web_edition/daily4.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/daily4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C313"/>
+  <dimension ref="A1:C314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8–3–9–6</t>
+          <t>1–7–9–1</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>05/26/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1–9–4–1</t>
+          <t>9–4–5–7</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/19/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0–4–9–1</t>
+          <t>9–4–2–8</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4–8–8–3</t>
+          <t>1–7–4–5</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7–4–5–0</t>
+          <t>9–3–1–0</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3–6–4–4</t>
+          <t>8–3–9–6</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3–3–2–1</t>
+          <t>1–9–4–1</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/19/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0–6–9–4</t>
+          <t>0–4–9–1</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/12/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5–4–2–3</t>
+          <t>4–8–8–3</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9–8–9–8</t>
+          <t>7–4–5–0</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5–7–1–9</t>
+          <t>3–6–4–4</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4–6–1–7</t>
+          <t>3–3–2–1</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7–7–9–9</t>
+          <t>0–6–9–4</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/06/2022</t>
+          <t>05/12/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7–9–4–2</t>
+          <t>5–4–2–3</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/05/2022</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4–7–6–9</t>
+          <t>9–8–9–8</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/04/2022</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3–8–5–3</t>
+          <t>5–7–1–9</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05/03/2022</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4–2–8–7</t>
+          <t>4–6–1–7</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9–9–3–2</t>
+          <t>7–7–9–9</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04/30/2022</t>
+          <t>05/06/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7–3–1–6</t>
+          <t>7–9–4–2</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/29/2022</t>
+          <t>05/05/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6–7–2–0</t>
+          <t>4–7–6–9</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04/28/2022</t>
+          <t>05/04/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8–8–0–9</t>
+          <t>3–8–5–3</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04/27/2022</t>
+          <t>05/03/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4–9–4–2</t>
+          <t>4–2–8–7</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>04/26/2022</t>
+          <t>05/02/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6–3–0–0</t>
+          <t>9–9–3–2</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/25/2022</t>
+          <t>04/30/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0–3–3–5</t>
+          <t>7–3–1–6</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04/23/2022</t>
+          <t>04/29/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4–2–7–9</t>
+          <t>6–7–2–0</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04/22/2022</t>
+          <t>04/28/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7–4–4–0</t>
+          <t>8–8–0–9</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04/21/2022</t>
+          <t>04/27/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>8–7–7–5</t>
+          <t>4–9–4–2</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04/20/2022</t>
+          <t>04/26/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5–6–2–8</t>
+          <t>6–3–0–0</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>04/19/2022</t>
+          <t>04/25/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5–6–9–6</t>
+          <t>0–3–3–5</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>04/18/2022</t>
+          <t>04/23/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0–5–7–7</t>
+          <t>4–2–7–9</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>04/16/2022</t>
+          <t>04/22/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5–8–5–3</t>
+          <t>7–4–4–0</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>04/15/2022</t>
+          <t>04/21/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0–6–8–2</t>
+          <t>8–7–7–5</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>04/14/2022</t>
+          <t>04/20/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8–2–9–7</t>
+          <t>5–6–2–8</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>04/13/2022</t>
+          <t>04/19/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7–4–3–7</t>
+          <t>5–6–9–6</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>04/12/2022</t>
+          <t>04/18/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3–8–9–3</t>
+          <t>0–5–7–7</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>04/11/2022</t>
+          <t>04/16/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2–7–8–0</t>
+          <t>5–8–5–3</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04/09/2022</t>
+          <t>04/15/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9–5–2–7</t>
+          <t>0–6–8–2</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>04/08/2022</t>
+          <t>04/14/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7–5–1–7</t>
+          <t>8–2–9–7</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>04/07/2022</t>
+          <t>04/13/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4–0–8–8</t>
+          <t>7–4–3–7</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>04/06/2022</t>
+          <t>04/12/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3–3–4–7</t>
+          <t>3–8–9–3</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>04/05/2022</t>
+          <t>04/11/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9–1–9–2</t>
+          <t>2–7–8–0</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>04/04/2022</t>
+          <t>04/09/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>6–9–0–3</t>
+          <t>9–5–2–7</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>04/02/2022</t>
+          <t>04/08/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4–3–6–2</t>
+          <t>7–5–1–7</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04/01/2022</t>
+          <t>04/07/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9–6–0–8</t>
+          <t>4–0–8–8</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>03/31/2022</t>
+          <t>04/06/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7–9–5–1</t>
+          <t>3–3–4–7</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>03/30/2022</t>
+          <t>04/05/2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>6–8–0–2</t>
+          <t>9–1–9–2</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>03/29/2022</t>
+          <t>04/04/2022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8–0–5–6</t>
+          <t>6–9–0–3</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>03/28/2022</t>
+          <t>04/02/2022</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3–8–7–8</t>
+          <t>4–3–6–2</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>03/26/2022</t>
+          <t>04/01/2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9–2–6–2</t>
+          <t>9–6–0–8</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>03/25/2022</t>
+          <t>03/31/2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0–0–2–7</t>
+          <t>7–9–5–1</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>03/24/2022</t>
+          <t>03/30/2022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4–9–3–5</t>
+          <t>6–8–0–2</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>03/23/2022</t>
+          <t>03/29/2022</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2–0–8–8</t>
+          <t>8–0–5–6</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>03/22/2022</t>
+          <t>03/28/2022</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5–6–6–6</t>
+          <t>3–8–7–8</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>03/21/2022</t>
+          <t>03/26/2022</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9–5–5–2</t>
+          <t>9–2–6–2</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>03/19/2022</t>
+          <t>03/25/2022</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1–1–4–0</t>
+          <t>0–0–2–7</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>03/18/2022</t>
+          <t>03/24/2022</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>4–0–0–3</t>
+          <t>4–9–3–5</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>03/17/2022</t>
+          <t>03/23/2022</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0–5–5–2</t>
+          <t>2–0–8–8</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>03/16/2022</t>
+          <t>03/22/2022</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1–7–7–4</t>
+          <t>5–6–6–6</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>03/15/2022</t>
+          <t>03/21/2022</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0–9–4–9</t>
+          <t>9–5–5–2</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>03/14/2022</t>
+          <t>03/19/2022</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>5–8–8–6</t>
+          <t>1–1–4–0</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>03/12/2022</t>
+          <t>03/18/2022</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>6–2–9–5</t>
+          <t>4–0–0–3</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>03/11/2022</t>
+          <t>03/17/2022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8–3–9–0</t>
+          <t>0–5–5–2</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>03/10/2022</t>
+          <t>03/16/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1–8–4–6</t>
+          <t>1–7–7–4</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>03/09/2022</t>
+          <t>03/15/2022</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4–8–9–1</t>
+          <t>0–9–4–9</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>03/08/2022</t>
+          <t>03/14/2022</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1–8–6–2</t>
+          <t>5–8–8–6</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>03/07/2022</t>
+          <t>03/12/2022</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2–1–0–3</t>
+          <t>6–2–9–5</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>03/11/2022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>8–2–5–0</t>
+          <t>8–3–9–0</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>03/04/2022</t>
+          <t>03/10/2022</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9–6–5–6</t>
+          <t>1–8–4–6</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>03/03/2022</t>
+          <t>03/09/2022</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3–6–5–5</t>
+          <t>4–8–9–1</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>03/02/2022</t>
+          <t>03/08/2022</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>8–6–1–3</t>
+          <t>1–8–6–2</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>03/07/2022</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0–3–0–4</t>
+          <t>2–1–0–3</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>02/28/2022</t>
+          <t>03/05/2022</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2–1–2–7</t>
+          <t>8–2–5–0</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>02/26/2022</t>
+          <t>03/04/2022</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1–9–6–0</t>
+          <t>9–6–5–6</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>02/25/2022</t>
+          <t>03/03/2022</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1–4–3–8</t>
+          <t>3–6–5–5</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>02/24/2022</t>
+          <t>03/02/2022</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5–7–1–0</t>
+          <t>8–6–1–3</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>02/23/2022</t>
+          <t>03/01/2022</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>8–3–8–2</t>
+          <t>0–3–0–4</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>02/22/2022</t>
+          <t>02/28/2022</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6–0–5–1</t>
+          <t>2–1–2–7</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>02/21/2022</t>
+          <t>02/26/2022</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8–4–1–4</t>
+          <t>1–9–6–0</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>02/19/2022</t>
+          <t>02/25/2022</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2–8–5–2</t>
+          <t>1–4–3–8</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>02/18/2022</t>
+          <t>02/24/2022</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>4–5–1–7</t>
+          <t>5–7–1–0</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>02/17/2022</t>
+          <t>02/23/2022</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1–7–3–8</t>
+          <t>8–3–8–2</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>02/16/2022</t>
+          <t>02/22/2022</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2–5–3–1</t>
+          <t>6–0–5–1</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>02/15/2022</t>
+          <t>02/21/2022</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1–1–4–7</t>
+          <t>8–4–1–4</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>02/14/2022</t>
+          <t>02/19/2022</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4–5–4–8</t>
+          <t>2–8–5–2</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>02/12/2022</t>
+          <t>02/18/2022</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>8–6–7–6</t>
+          <t>4–5–1–7</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>02/11/2022</t>
+          <t>02/17/2022</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0–1–3–0</t>
+          <t>1–7–3–8</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>02/10/2022</t>
+          <t>02/16/2022</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>7–3–7–4</t>
+          <t>2–5–3–1</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>02/15/2022</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9–7–1–8</t>
+          <t>1–1–4–7</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>02/08/2022</t>
+          <t>02/14/2022</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>8–7–3–6</t>
+          <t>4–5–4–8</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>02/07/2022</t>
+          <t>02/12/2022</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2–4–4–3</t>
+          <t>8–6–7–6</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>02/05/2022</t>
+          <t>02/11/2022</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>6–4–1–0</t>
+          <t>0–1–3–0</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>02/04/2022</t>
+          <t>02/10/2022</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1–0–9–7</t>
+          <t>7–3–7–4</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>02/03/2022</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>8–4–3–0</t>
+          <t>9–7–1–8</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>02/02/2022</t>
+          <t>02/08/2022</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3–0–9–4</t>
+          <t>8–7–3–6</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>02/01/2022</t>
+          <t>02/07/2022</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4–0–0–7</t>
+          <t>2–4–4–3</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01/31/2022</t>
+          <t>02/05/2022</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1–9–3–5</t>
+          <t>6–4–1–0</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01/29/2022</t>
+          <t>02/04/2022</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>6–9–0–0</t>
+          <t>1–0–9–7</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01/28/2022</t>
+          <t>02/03/2022</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>5–2–9–3</t>
+          <t>8–4–3–0</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01/27/2022</t>
+          <t>02/02/2022</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>7–4–9–7</t>
+          <t>3–0–9–4</t>
         </is>
       </c>
     </row>
@@ -1931,12 +1931,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01/26/2022</t>
+          <t>02/01/2022</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3–8–5–4</t>
+          <t>4–0–0–7</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01/25/2022</t>
+          <t>01/31/2022</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>4–5–7–6</t>
+          <t>1–9–3–5</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01/24/2022</t>
+          <t>01/29/2022</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0–4–7–7</t>
+          <t>6–9–0–0</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01/22/2022</t>
+          <t>01/28/2022</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1–7–1–8</t>
+          <t>5–2–9–3</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1991,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01/21/2022</t>
+          <t>01/27/2022</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2–2–8–4</t>
+          <t>7–4–9–7</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01/20/2022</t>
+          <t>01/26/2022</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>9–6–6–3</t>
+          <t>3–8–5–4</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01/19/2022</t>
+          <t>01/25/2022</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1–1–9–5</t>
+          <t>4–5–7–6</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01/18/2022</t>
+          <t>01/24/2022</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>5–0–2–7</t>
+          <t>0–4–7–7</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01/17/2022</t>
+          <t>01/22/2022</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>5–6–5–6</t>
+          <t>1–7–1–8</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01/15/2022</t>
+          <t>01/21/2022</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>6–8–6–5</t>
+          <t>2–2–8–4</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01/14/2022</t>
+          <t>01/20/2022</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>5–7–4–6</t>
+          <t>9–6–6–3</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01/13/2022</t>
+          <t>01/19/2022</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>6–1–6–2</t>
+          <t>1–1–9–5</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01/12/2022</t>
+          <t>01/18/2022</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>8–5–9–3</t>
+          <t>5–0–2–7</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01/11/2022</t>
+          <t>01/17/2022</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>6–8–6–9</t>
+          <t>5–6–5–6</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/15/2022</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>9–3–7–2</t>
+          <t>6–8–6–5</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01/08/2022</t>
+          <t>01/14/2022</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>4–7–3–7</t>
+          <t>5–7–4–6</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/13/2022</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2–4–6–5</t>
+          <t>6–1–6–2</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01/06/2022</t>
+          <t>01/12/2022</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>8–9–3–2</t>
+          <t>8–5–9–3</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01/05/2022</t>
+          <t>01/11/2022</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>7–0–7–3</t>
+          <t>6–8–6–9</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>9–4–8–7</t>
+          <t>9–3–7–2</t>
         </is>
       </c>
     </row>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01/03/2022</t>
+          <t>01/08/2022</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>8–1–2–2</t>
+          <t>4–7–3–7</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>8–0–7–2</t>
+          <t>2–4–6–5</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>01/06/2022</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>4–2–6–5</t>
+          <t>8–9–3–2</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>12/30/2021</t>
+          <t>01/05/2022</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2–8–4–6</t>
+          <t>7–0–7–3</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12/29/2021</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2–6–9–0</t>
+          <t>9–4–8–7</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>12/28/2021</t>
+          <t>01/03/2022</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>9–2–6–9</t>
+          <t>8–1–2–2</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>12/27/2021</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>9–6–3–7</t>
+          <t>8–0–7–2</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>12/25/2021</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1–3–6–7</t>
+          <t>4–2–6–5</t>
         </is>
       </c>
     </row>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>12/24/2021</t>
+          <t>12/30/2021</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>7–9–3–6</t>
+          <t>2–8–4–6</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12/23/2021</t>
+          <t>12/29/2021</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>5–8–8–1</t>
+          <t>2–6–9–0</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>12/22/2021</t>
+          <t>12/28/2021</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>7–1–5–6</t>
+          <t>9–2–6–9</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>12/21/2021</t>
+          <t>12/27/2021</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>5–4–4–9</t>
+          <t>9–6–3–7</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>12/20/2021</t>
+          <t>12/25/2021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>6–4–7–8</t>
+          <t>1–3–6–7</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>12/18/2021</t>
+          <t>12/24/2021</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>7–7–1–3</t>
+          <t>7–9–3–6</t>
         </is>
       </c>
     </row>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>12/17/2021</t>
+          <t>12/23/2021</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1–8–8–2</t>
+          <t>5–8–8–1</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>12/16/2021</t>
+          <t>12/22/2021</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>5–4–0–6</t>
+          <t>7–1–5–6</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>12/15/2021</t>
+          <t>12/21/2021</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0–1–4–9</t>
+          <t>5–4–4–9</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>12/14/2021</t>
+          <t>12/20/2021</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>4–7–7–2</t>
+          <t>6–4–7–8</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>12/13/2021</t>
+          <t>12/18/2021</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>9–3–8–3</t>
+          <t>7–7–1–3</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>12/11/2021</t>
+          <t>12/17/2021</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>5–3–3–8</t>
+          <t>1–8–8–2</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>12/10/2021</t>
+          <t>12/16/2021</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>8–3–2–4</t>
+          <t>5–4–0–6</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>12/09/2021</t>
+          <t>12/15/2021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2–6–0–3</t>
+          <t>0–1–4–9</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>12/14/2021</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>6–3–4–4</t>
+          <t>4–7–7–2</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>12/13/2021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1–0–0–9</t>
+          <t>9–3–8–3</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2591,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>12/06/2021</t>
+          <t>12/11/2021</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>4–5–3–9</t>
+          <t>5–3–3–8</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>12/04/2021</t>
+          <t>12/10/2021</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2–5–6–0</t>
+          <t>8–3–2–4</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>12/03/2021</t>
+          <t>12/09/2021</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>6–8–8–4</t>
+          <t>2–6–0–3</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>12/02/2021</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>8–2–9–5</t>
+          <t>6–3–4–4</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>12/01/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>5–5–9–9</t>
+          <t>1–0–0–9</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>11/30/2021</t>
+          <t>12/06/2021</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>6–9–4–7</t>
+          <t>4–5–3–9</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>11/29/2021</t>
+          <t>12/04/2021</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>8–0–3–1</t>
+          <t>2–5–6–0</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>11/27/2021</t>
+          <t>12/03/2021</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>8–1–5–3</t>
+          <t>6–8–8–4</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>11/26/2021</t>
+          <t>12/02/2021</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>8–2–7–2</t>
+          <t>8–2–9–5</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>11/25/2021</t>
+          <t>12/01/2021</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>1–2–0–5</t>
+          <t>5–5–9–9</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>11/24/2021</t>
+          <t>11/30/2021</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>4–3–9–3</t>
+          <t>6–9–4–7</t>
         </is>
       </c>
     </row>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>11/23/2021</t>
+          <t>11/29/2021</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>4–8–1–1</t>
+          <t>8–0–3–1</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>11/22/2021</t>
+          <t>11/27/2021</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0–8–0–5</t>
+          <t>8–1–5–3</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>11/20/2021</t>
+          <t>11/26/2021</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>1–9–4–3</t>
+          <t>8–2–7–2</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>11/19/2021</t>
+          <t>11/25/2021</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5–3–4–6</t>
+          <t>1–2–0–5</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>11/18/2021</t>
+          <t>11/24/2021</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2–1–0–5</t>
+          <t>4–3–9–3</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>11/17/2021</t>
+          <t>11/23/2021</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>8–8–6–5</t>
+          <t>4–8–1–1</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2846,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>11/16/2021</t>
+          <t>11/22/2021</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>7–0–7–3</t>
+          <t>0–8–0–5</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>11/15/2021</t>
+          <t>11/20/2021</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>6–8–2–4</t>
+          <t>1–9–4–3</t>
         </is>
       </c>
     </row>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>11/13/2021</t>
+          <t>11/19/2021</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>6–2–5–8</t>
+          <t>5–3–4–6</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>11/12/2021</t>
+          <t>11/18/2021</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>1–5–5–6</t>
+          <t>2–1–0–5</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>11/11/2021</t>
+          <t>11/17/2021</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>0–9–9–0</t>
+          <t>8–8–6–5</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>11/10/2021</t>
+          <t>11/16/2021</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>4–5–1–2</t>
+          <t>7–0–7–3</t>
         </is>
       </c>
     </row>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>11/09/2021</t>
+          <t>11/15/2021</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>6–3–9–5</t>
+          <t>6–8–2–4</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>11/08/2021</t>
+          <t>11/13/2021</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>0–6–4–1</t>
+          <t>6–2–5–8</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>11/06/2021</t>
+          <t>11/12/2021</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>9–4–6–1</t>
+          <t>1–5–5–6</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>11/05/2021</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>4–6–5–2</t>
+          <t>0–9–9–0</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>11/04/2021</t>
+          <t>11/10/2021</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9–6–4–5</t>
+          <t>4–5–1–2</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>11/09/2021</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1–2–2–7</t>
+          <t>6–3–9–5</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>11/02/2021</t>
+          <t>11/08/2021</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>4–0–7–2</t>
+          <t>0–6–4–1</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>11/01/2021</t>
+          <t>11/06/2021</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>7–1–0–8</t>
+          <t>9–4–6–1</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>10/30/2021</t>
+          <t>11/05/2021</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>8–2–0–5</t>
+          <t>4–6–5–2</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>10/29/2021</t>
+          <t>11/04/2021</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>5–5–3–5</t>
+          <t>9–6–4–5</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>10/28/2021</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>6–5–9–9</t>
+          <t>1–2–2–7</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>10/27/2021</t>
+          <t>11/02/2021</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>5–7–3–3</t>
+          <t>4–0–7–2</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>10/26/2021</t>
+          <t>11/01/2021</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>3–5–3–3</t>
+          <t>7–1–0–8</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>10/25/2021</t>
+          <t>10/30/2021</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>5–3–8–4</t>
+          <t>8–2–0–5</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>10/23/2021</t>
+          <t>10/29/2021</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>4–1–3–4</t>
+          <t>5–5–3–5</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>10/22/2021</t>
+          <t>10/28/2021</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0–5–5–2</t>
+          <t>6–5–9–9</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>10/21/2021</t>
+          <t>10/27/2021</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1–5–2–2</t>
+          <t>5–7–3–3</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>10/20/2021</t>
+          <t>10/26/2021</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1–8–9–5</t>
+          <t>3–5–3–3</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>10/19/2021</t>
+          <t>10/25/2021</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>6–7–3–8</t>
+          <t>5–3–8–4</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>10/18/2021</t>
+          <t>10/23/2021</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>5–4–3–2</t>
+          <t>4–1–3–4</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>10/16/2021</t>
+          <t>10/22/2021</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>5–3–2–8</t>
+          <t>0–5–5–2</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>10/15/2021</t>
+          <t>10/21/2021</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>6–7–3–5</t>
+          <t>1–5–2–2</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>10/14/2021</t>
+          <t>10/20/2021</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0–8–5–5</t>
+          <t>1–8–9–5</t>
         </is>
       </c>
     </row>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>10/13/2021</t>
+          <t>10/19/2021</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>0–4–9–6</t>
+          <t>6–7–3–8</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>10/12/2021</t>
+          <t>10/18/2021</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>5–0–4–5</t>
+          <t>5–4–3–2</t>
         </is>
       </c>
     </row>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>10/11/2021</t>
+          <t>10/16/2021</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>6–7–3–5</t>
+          <t>5–3–2–8</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>10/09/2021</t>
+          <t>10/15/2021</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>0–2–8–4</t>
+          <t>6–7–3–5</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>10/08/2021</t>
+          <t>10/14/2021</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>6–9–3–7</t>
+          <t>0–8–5–5</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>10/07/2021</t>
+          <t>10/13/2021</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>4–8–8–5</t>
+          <t>0–4–9–6</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>10/12/2021</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>6–5–3–8</t>
+          <t>5–0–4–5</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>10/05/2021</t>
+          <t>10/11/2021</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>0–3–3–1</t>
+          <t>6–7–3–5</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>10/04/2021</t>
+          <t>10/09/2021</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2–7–7–5</t>
+          <t>0–2–8–4</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>10/02/2021</t>
+          <t>10/08/2021</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>8–7–8–6</t>
+          <t>6–9–3–7</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>10/07/2021</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>9–7–2–2</t>
+          <t>4–8–8–5</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>09/30/2021</t>
+          <t>10/06/2021</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>7–3–7–2</t>
+          <t>6–5–3–8</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>09/29/2021</t>
+          <t>10/05/2021</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>9–5–3–5</t>
+          <t>0–3–3–1</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>09/28/2021</t>
+          <t>10/04/2021</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>5–1–8–5</t>
+          <t>2–7–7–5</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>10/02/2021</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>6–7–6–9</t>
+          <t>8–7–8–6</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>09/25/2021</t>
+          <t>10/01/2021</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>8–1–4–5</t>
+          <t>9–7–2–2</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>09/24/2021</t>
+          <t>09/30/2021</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>3–3–8–6</t>
+          <t>7–3–7–2</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>09/23/2021</t>
+          <t>09/29/2021</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>9–9–1–1</t>
+          <t>9–5–3–5</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>09/22/2021</t>
+          <t>09/28/2021</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>5–7–6–8</t>
+          <t>5–1–8–5</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>09/21/2021</t>
+          <t>09/27/2021</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>3–6–6–4</t>
+          <t>6–7–6–9</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>09/25/2021</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>1–9–4–4</t>
+          <t>8–1–4–5</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>09/18/2021</t>
+          <t>09/24/2021</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2–3–8–4</t>
+          <t>3–3–8–6</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>09/17/2021</t>
+          <t>09/23/2021</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>7–9–4–3</t>
+          <t>9–9–1–1</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>09/16/2021</t>
+          <t>09/22/2021</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>7–0–6–9</t>
+          <t>5–7–6–8</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3641,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>09/15/2021</t>
+          <t>09/21/2021</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2–9–0–1</t>
+          <t>3–6–6–4</t>
         </is>
       </c>
     </row>
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>09/14/2021</t>
+          <t>09/20/2021</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>6–8–5–0</t>
+          <t>1–9–4–4</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>09/13/2021</t>
+          <t>09/18/2021</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>7–2–1–3</t>
+          <t>2–3–8–4</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>09/11/2021</t>
+          <t>09/17/2021</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>4–1–2–1</t>
+          <t>7–9–4–3</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>09/10/2021</t>
+          <t>09/16/2021</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2–3–2–3</t>
+          <t>7–0–6–9</t>
         </is>
       </c>
     </row>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>09/09/2021</t>
+          <t>09/15/2021</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>0–5–5–4</t>
+          <t>2–9–0–1</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>09/08/2021</t>
+          <t>09/14/2021</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>7–5–5–5</t>
+          <t>6–8–5–0</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>09/13/2021</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>7–8–2–1</t>
+          <t>7–2–1–3</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>09/06/2021</t>
+          <t>09/11/2021</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>7–2–6–9</t>
+          <t>4–1–2–1</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3776,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>09/04/2021</t>
+          <t>09/10/2021</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>7–6–9–3</t>
+          <t>2–3–2–3</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>09/03/2021</t>
+          <t>09/09/2021</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>7–0–3–4</t>
+          <t>0–5–5–4</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1–2–1–2</t>
+          <t>7–5–5–5</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>09/01/2021</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1–7–4–9</t>
+          <t>7–8–2–1</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3836,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>08/31/2021</t>
+          <t>09/06/2021</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>8–2–1–4</t>
+          <t>7–2–6–9</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
+          <t>09/04/2021</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>9–7–7–0</t>
+          <t>7–6–9–3</t>
         </is>
       </c>
     </row>
@@ -3866,12 +3866,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>08/28/2021</t>
+          <t>09/03/2021</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>3–0–3–3</t>
+          <t>7–0–3–4</t>
         </is>
       </c>
     </row>
@@ -3881,12 +3881,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>08/27/2021</t>
+          <t>09/02/2021</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>0–1–2–3</t>
+          <t>1–2–1–2</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>08/26/2021</t>
+          <t>09/01/2021</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>8–5–5–2</t>
+          <t>1–7–4–9</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>08/25/2021</t>
+          <t>08/31/2021</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>5–6–7–8</t>
+          <t>8–2–1–4</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>08/24/2021</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2–4–2–8</t>
+          <t>9–7–7–0</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>08/23/2021</t>
+          <t>08/28/2021</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>1–6–7–5</t>
+          <t>3–0–3–3</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>08/21/2021</t>
+          <t>08/27/2021</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0–8–0–2</t>
+          <t>0–1–2–3</t>
         </is>
       </c>
     </row>
@@ -3971,12 +3971,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>08/20/2021</t>
+          <t>08/26/2021</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>7–9–9–1</t>
+          <t>8–5–5–2</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>08/19/2021</t>
+          <t>08/25/2021</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>8–4–6–8</t>
+          <t>5–6–7–8</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>08/18/2021</t>
+          <t>08/24/2021</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>4–5–0–9</t>
+          <t>2–4–2–8</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4016,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>08/17/2021</t>
+          <t>08/23/2021</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>3–2–7–1</t>
+          <t>1–6–7–5</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>08/16/2021</t>
+          <t>08/21/2021</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>8–4–4–8</t>
+          <t>0–8–0–2</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>08/14/2021</t>
+          <t>08/20/2021</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>7–0–3–0</t>
+          <t>7–9–9–1</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>08/13/2021</t>
+          <t>08/19/2021</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0–7–3–8</t>
+          <t>8–4–6–8</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>08/12/2021</t>
+          <t>08/18/2021</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>3–1–5–2</t>
+          <t>4–5–0–9</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>08/11/2021</t>
+          <t>08/17/2021</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>7–5–9–0</t>
+          <t>3–2–7–1</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>08/10/2021</t>
+          <t>08/16/2021</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>7–2–6–1</t>
+          <t>8–4–4–8</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>08/09/2021</t>
+          <t>08/14/2021</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1–1–1–1</t>
+          <t>7–0–3–0</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>08/07/2021</t>
+          <t>08/13/2021</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>7–0–0–7</t>
+          <t>0–7–3–8</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>08/12/2021</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>0–2–7–5</t>
+          <t>3–1–5–2</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>08/05/2021</t>
+          <t>08/11/2021</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>5–0–5–3</t>
+          <t>7–5–9–0</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>08/04/2021</t>
+          <t>08/10/2021</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>0–9–2–9</t>
+          <t>7–2–6–1</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4196,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>08/03/2021</t>
+          <t>08/09/2021</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>1–2–2–6</t>
+          <t>1–1–1–1</t>
         </is>
       </c>
     </row>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>08/02/2021</t>
+          <t>08/07/2021</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>5–1–4–0</t>
+          <t>7–0–0–7</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>07/31/2021</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>9–5–8–8</t>
+          <t>0–2–7–5</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>07/30/2021</t>
+          <t>08/05/2021</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>9–6–7–8</t>
+          <t>5–0–5–3</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>07/29/2021</t>
+          <t>08/04/2021</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>8–1–5–5</t>
+          <t>0–9–2–9</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>07/28/2021</t>
+          <t>08/03/2021</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>0–1–3–8</t>
+          <t>1–2–2–6</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>07/27/2021</t>
+          <t>08/02/2021</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>8–7–6–6</t>
+          <t>5–1–4–0</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>07/26/2021</t>
+          <t>07/31/2021</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1–2–7–3</t>
+          <t>9–5–8–8</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>07/24/2021</t>
+          <t>07/30/2021</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>8–5–0–4</t>
+          <t>9–6–7–8</t>
         </is>
       </c>
     </row>
@@ -4331,12 +4331,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>07/23/2021</t>
+          <t>07/29/2021</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>9–8–9–2</t>
+          <t>8–1–5–5</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>07/22/2021</t>
+          <t>07/28/2021</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>3–4–6–0</t>
+          <t>0–1–3–8</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>07/21/2021</t>
+          <t>07/27/2021</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>9–6–1–6</t>
+          <t>8–7–6–6</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4376,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>07/26/2021</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>6–7–1–6</t>
+          <t>1–2–7–3</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>07/19/2021</t>
+          <t>07/24/2021</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>1–6–6–7</t>
+          <t>8–5–0–4</t>
         </is>
       </c>
     </row>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>07/17/2021</t>
+          <t>07/23/2021</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>6–7–6–5</t>
+          <t>9–8–9–2</t>
         </is>
       </c>
     </row>
@@ -4421,12 +4421,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>07/16/2021</t>
+          <t>07/22/2021</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>3–3–0–3</t>
+          <t>3–4–6–0</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>07/15/2021</t>
+          <t>07/21/2021</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>3–2–8–2</t>
+          <t>9–6–1–6</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>07/14/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>3–4–8–8</t>
+          <t>6–7–1–6</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>07/13/2021</t>
+          <t>07/19/2021</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2–8–6–3</t>
+          <t>1–6–6–7</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>07/12/2021</t>
+          <t>07/17/2021</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>1–7–4–2</t>
+          <t>6–7–6–5</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>07/10/2021</t>
+          <t>07/16/2021</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>6–7–1–2</t>
+          <t>3–3–0–3</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>07/09/2021</t>
+          <t>07/15/2021</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>7–0–5–2</t>
+          <t>3–2–8–2</t>
         </is>
       </c>
     </row>
@@ -4526,12 +4526,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>07/08/2021</t>
+          <t>07/14/2021</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>7–8–5–3</t>
+          <t>3–4–8–8</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>07/07/2021</t>
+          <t>07/13/2021</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>1–8–3–3</t>
+          <t>2–8–6–3</t>
         </is>
       </c>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>07/12/2021</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>9–6–8–2</t>
+          <t>1–7–4–2</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>07/05/2021</t>
+          <t>07/10/2021</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>1–3–3–6</t>
+          <t>6–7–1–2</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>07/03/2021</t>
+          <t>07/09/2021</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>5–6–1–4</t>
+          <t>7–0–5–2</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>07/02/2021</t>
+          <t>07/08/2021</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4–6–8–8</t>
+          <t>7–8–5–3</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>07/01/2021</t>
+          <t>07/07/2021</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>9–5–0–9</t>
+          <t>1–8–3–3</t>
         </is>
       </c>
     </row>
@@ -4631,12 +4631,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>06/30/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>6–0–5–6</t>
+          <t>9–6–8–2</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>07/05/2021</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4–4–8–1</t>
+          <t>1–3–3–6</t>
         </is>
       </c>
     </row>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>06/28/2021</t>
+          <t>07/03/2021</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7–7–0–1</t>
+          <t>5–6–1–4</t>
         </is>
       </c>
     </row>
@@ -4676,12 +4676,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>06/26/2021</t>
+          <t>07/02/2021</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>6–1–4–9</t>
+          <t>4–6–8–8</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>06/25/2021</t>
+          <t>07/01/2021</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>7–8–8–9</t>
+          <t>9–5–0–9</t>
         </is>
       </c>
     </row>
@@ -4706,12 +4706,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>06/24/2021</t>
+          <t>06/30/2021</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>6–2–4–7</t>
+          <t>6–0–5–6</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>06/23/2021</t>
+          <t>06/29/2021</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>9–0–6–3</t>
+          <t>4–4–8–1</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>06/22/2021</t>
+          <t>06/28/2021</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>1–6–1–3</t>
+          <t>7–7–0–1</t>
         </is>
       </c>
     </row>
@@ -4751,12 +4751,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>06/21/2021</t>
+          <t>06/26/2021</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>1–1–5–9</t>
+          <t>6–1–4–9</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>06/19/2021</t>
+          <t>06/25/2021</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>5–8–3–5</t>
+          <t>7–8–8–9</t>
         </is>
       </c>
     </row>
@@ -4781,12 +4781,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>06/18/2021</t>
+          <t>06/24/2021</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>6–1–0–2</t>
+          <t>6–2–4–7</t>
         </is>
       </c>
     </row>
@@ -4796,12 +4796,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>06/17/2021</t>
+          <t>06/23/2021</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>1–7–3–4</t>
+          <t>9–0–6–3</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>06/16/2021</t>
+          <t>06/22/2021</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>6–6–5–0</t>
+          <t>1–6–1–3</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>06/15/2021</t>
+          <t>06/21/2021</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>6–8–8–3</t>
+          <t>1–1–5–9</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>06/14/2021</t>
+          <t>06/19/2021</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2–7–2–1</t>
+          <t>5–8–3–5</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4856,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>06/12/2021</t>
+          <t>06/18/2021</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>7–2–4–6</t>
+          <t>6–1–0–2</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4871,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>06/11/2021</t>
+          <t>06/17/2021</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0–3–0–4</t>
+          <t>1–7–3–4</t>
         </is>
       </c>
     </row>
@@ -4886,12 +4886,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>06/10/2021</t>
+          <t>06/16/2021</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>4–2–8–0</t>
+          <t>6–6–5–0</t>
         </is>
       </c>
     </row>
@@ -4901,12 +4901,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>06/09/2021</t>
+          <t>06/15/2021</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>8–0–4–0</t>
+          <t>6–8–8–3</t>
         </is>
       </c>
     </row>
@@ -4916,12 +4916,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>06/08/2021</t>
+          <t>06/14/2021</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>3–9–6–8</t>
+          <t>2–7–2–1</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>06/07/2021</t>
+          <t>06/12/2021</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>5–6–2–5</t>
+          <t>7–2–4–6</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>06/05/2021</t>
+          <t>06/11/2021</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>6–7–7–2</t>
+          <t>0–3–0–4</t>
         </is>
       </c>
     </row>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
+          <t>06/10/2021</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>6–3–8–1</t>
+          <t>4–2–8–0</t>
         </is>
       </c>
     </row>
@@ -4976,12 +4976,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>06/03/2021</t>
+          <t>06/09/2021</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>1–5–8–4</t>
+          <t>8–0–4–0</t>
         </is>
       </c>
     </row>
@@ -4991,12 +4991,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>06/08/2021</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>8–1–9–1</t>
+          <t>3–9–6–8</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>06/01/2021</t>
+          <t>06/07/2021</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>9–6–3–0</t>
+          <t>5–6–2–5</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>05/31/2021</t>
+          <t>06/05/2021</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>1–2–8–3</t>
+          <t>6–7–7–2</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>05/29/2021</t>
+          <t>06/04/2021</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>5–9–0–4</t>
+          <t>6–3–8–1</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>05/28/2021</t>
+          <t>06/03/2021</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>4–6–0–9</t>
+          <t>1–5–8–4</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>05/27/2021</t>
+          <t>06/02/2021</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>0–5–5–2</t>
+          <t>8–1–9–1</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>05/26/2021</t>
+          <t>06/01/2021</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1–8–9–1</t>
+          <t>9–6–3–0</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5096,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>05/25/2021</t>
+          <t>05/31/2021</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>5–8–4–0</t>
+          <t>1–2–8–3</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5111,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>05/24/2021</t>
+          <t>05/29/2021</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>1–0–9–1</t>
+          <t>5–9–0–4</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>312</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>05/28/2021</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>4–6–0–9</t>
         </is>
       </c>
     </row>

--- a/lottopy_site/lottopy/lottopy_web_edition/daily4.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/daily4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C314"/>
+  <dimension ref="A1:C315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05/27/2022</t>
+          <t>06/08/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1–7–9–1</t>
+          <t>7–2–5–5</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05/26/2022</t>
+          <t>06/07/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9–4–5–7</t>
+          <t>1–3–3–5</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/25/2022</t>
+          <t>06/06/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9–4–2–8</t>
+          <t>1–0–4–2</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/24/2022</t>
+          <t>06/04/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1–7–4–5</t>
+          <t>5–3–1–8</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/23/2022</t>
+          <t>06/03/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9–3–1–0</t>
+          <t>3–6–2–7</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>06/02/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8–3–9–6</t>
+          <t>2–9–0–1</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>06/01/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1–9–4–1</t>
+          <t>4–2–3–3</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/19/2022</t>
+          <t>05/31/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0–4–9–1</t>
+          <t>4–0–8–3</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/30/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4–8–8–3</t>
+          <t>5–8–1–0</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/28/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7–4–5–0</t>
+          <t>4–9–7–6</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3–6–4–4</t>
+          <t>1–7–9–1</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/26/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3–3–2–1</t>
+          <t>9–4–5–7</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0–6–9–4</t>
+          <t>9–4–2–8</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/12/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5–4–2–3</t>
+          <t>1–7–4–5</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9–8–9–8</t>
+          <t>9–3–1–0</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5–7–1–9</t>
+          <t>8–3–9–6</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4–6–1–7</t>
+          <t>1–9–4–1</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>05/19/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7–7–9–9</t>
+          <t>0–4–9–1</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>05/06/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7–9–4–2</t>
+          <t>4–8–8–3</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05/05/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4–7–6–9</t>
+          <t>7–4–5–0</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05/04/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3–8–5–3</t>
+          <t>3–6–4–4</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05/03/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4–2–8–7</t>
+          <t>3–3–2–1</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9–9–3–2</t>
+          <t>0–6–9–4</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/30/2022</t>
+          <t>05/12/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7–3–1–6</t>
+          <t>5–4–2–3</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04/29/2022</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6–7–2–0</t>
+          <t>9–8–9–8</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04/28/2022</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8–8–0–9</t>
+          <t>5–7–1–9</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04/27/2022</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4–9–4–2</t>
+          <t>4–6–1–7</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04/26/2022</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6–3–0–0</t>
+          <t>7–7–9–9</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>04/25/2022</t>
+          <t>05/06/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0–3–3–5</t>
+          <t>7–9–4–2</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>04/23/2022</t>
+          <t>05/05/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4–2–7–9</t>
+          <t>4–7–6–9</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>04/22/2022</t>
+          <t>05/04/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7–4–4–0</t>
+          <t>3–8–5–3</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>04/21/2022</t>
+          <t>05/03/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8–7–7–5</t>
+          <t>4–2–8–7</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>04/20/2022</t>
+          <t>05/02/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5–6–2–8</t>
+          <t>9–9–3–2</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>04/19/2022</t>
+          <t>04/30/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5–6–9–6</t>
+          <t>7–3–1–6</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>04/18/2022</t>
+          <t>04/29/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0–5–7–7</t>
+          <t>6–7–2–0</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>04/16/2022</t>
+          <t>04/28/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5–8–5–3</t>
+          <t>8–8–0–9</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04/15/2022</t>
+          <t>04/27/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0–6–8–2</t>
+          <t>4–9–4–2</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>04/14/2022</t>
+          <t>04/26/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>8–2–9–7</t>
+          <t>6–3–0–0</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>04/13/2022</t>
+          <t>04/25/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7–4–3–7</t>
+          <t>0–3–3–5</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>04/12/2022</t>
+          <t>04/23/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3–8–9–3</t>
+          <t>4–2–7–9</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>04/11/2022</t>
+          <t>04/22/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2–7–8–0</t>
+          <t>7–4–4–0</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>04/09/2022</t>
+          <t>04/21/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9–5–2–7</t>
+          <t>8–7–7–5</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>04/08/2022</t>
+          <t>04/20/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7–5–1–7</t>
+          <t>5–6–2–8</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04/07/2022</t>
+          <t>04/19/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4–0–8–8</t>
+          <t>5–6–9–6</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>04/06/2022</t>
+          <t>04/18/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3–3–4–7</t>
+          <t>0–5–7–7</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>04/05/2022</t>
+          <t>04/16/2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9–1–9–2</t>
+          <t>5–8–5–3</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>04/04/2022</t>
+          <t>04/15/2022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6–9–0–3</t>
+          <t>0–6–8–2</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>04/02/2022</t>
+          <t>04/14/2022</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>4–3–6–2</t>
+          <t>8–2–9–7</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>04/01/2022</t>
+          <t>04/13/2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>9–6–0–8</t>
+          <t>7–4–3–7</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>03/31/2022</t>
+          <t>04/12/2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>7–9–5–1</t>
+          <t>3–8–9–3</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>03/30/2022</t>
+          <t>04/11/2022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6–8–0–2</t>
+          <t>2–7–8–0</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>03/29/2022</t>
+          <t>04/09/2022</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8–0–5–6</t>
+          <t>9–5–2–7</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>03/28/2022</t>
+          <t>04/08/2022</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3–8–7–8</t>
+          <t>7–5–1–7</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>03/26/2022</t>
+          <t>04/07/2022</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>9–2–6–2</t>
+          <t>4–0–8–8</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>03/25/2022</t>
+          <t>04/06/2022</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0–0–2–7</t>
+          <t>3–3–4–7</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>03/24/2022</t>
+          <t>04/05/2022</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>4–9–3–5</t>
+          <t>9–1–9–2</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>03/23/2022</t>
+          <t>04/04/2022</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2–0–8–8</t>
+          <t>6–9–0–3</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>03/22/2022</t>
+          <t>04/02/2022</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5–6–6–6</t>
+          <t>4–3–6–2</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>03/21/2022</t>
+          <t>04/01/2022</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9–5–5–2</t>
+          <t>9–6–0–8</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>03/19/2022</t>
+          <t>03/31/2022</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1–1–4–0</t>
+          <t>7–9–5–1</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>03/18/2022</t>
+          <t>03/30/2022</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>4–0–0–3</t>
+          <t>6–8–0–2</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>03/17/2022</t>
+          <t>03/29/2022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0–5–5–2</t>
+          <t>8–0–5–6</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>03/16/2022</t>
+          <t>03/28/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1–7–7–4</t>
+          <t>3–8–7–8</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>03/15/2022</t>
+          <t>03/26/2022</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0–9–4–9</t>
+          <t>9–2–6–2</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>03/14/2022</t>
+          <t>03/25/2022</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>5–8–8–6</t>
+          <t>0–0–2–7</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>03/12/2022</t>
+          <t>03/24/2022</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6–2–9–5</t>
+          <t>4–9–3–5</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>03/11/2022</t>
+          <t>03/23/2022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>8–3–9–0</t>
+          <t>2–0–8–8</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>03/10/2022</t>
+          <t>03/22/2022</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1–8–4–6</t>
+          <t>5–6–6–6</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>03/09/2022</t>
+          <t>03/21/2022</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>4–8–9–1</t>
+          <t>9–5–5–2</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>03/08/2022</t>
+          <t>03/19/2022</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1–8–6–2</t>
+          <t>1–1–4–0</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>03/07/2022</t>
+          <t>03/18/2022</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2–1–0–3</t>
+          <t>4–0–0–3</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>03/17/2022</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>8–2–5–0</t>
+          <t>0–5–5–2</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>03/04/2022</t>
+          <t>03/16/2022</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9–6–5–6</t>
+          <t>1–7–7–4</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>03/03/2022</t>
+          <t>03/15/2022</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3–6–5–5</t>
+          <t>0–9–4–9</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>03/02/2022</t>
+          <t>03/14/2022</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>8–6–1–3</t>
+          <t>5–8–8–6</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>03/12/2022</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0–3–0–4</t>
+          <t>6–2–9–5</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>02/28/2022</t>
+          <t>03/11/2022</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2–1–2–7</t>
+          <t>8–3–9–0</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>02/26/2022</t>
+          <t>03/10/2022</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1–9–6–0</t>
+          <t>1–8–4–6</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>02/25/2022</t>
+          <t>03/09/2022</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1–4–3–8</t>
+          <t>4–8–9–1</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>02/24/2022</t>
+          <t>03/08/2022</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>5–7–1–0</t>
+          <t>1–8–6–2</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>02/23/2022</t>
+          <t>03/07/2022</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>8–3–8–2</t>
+          <t>2–1–0–3</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>02/22/2022</t>
+          <t>03/05/2022</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6–0–5–1</t>
+          <t>8–2–5–0</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>02/21/2022</t>
+          <t>03/04/2022</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>8–4–1–4</t>
+          <t>9–6–5–6</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>02/19/2022</t>
+          <t>03/03/2022</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2–8–5–2</t>
+          <t>3–6–5–5</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>02/18/2022</t>
+          <t>03/02/2022</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4–5–1–7</t>
+          <t>8–6–1–3</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>02/17/2022</t>
+          <t>03/01/2022</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1–7–3–8</t>
+          <t>0–3–0–4</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>02/16/2022</t>
+          <t>02/28/2022</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2–5–3–1</t>
+          <t>2–1–2–7</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>02/15/2022</t>
+          <t>02/26/2022</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1–1–4–7</t>
+          <t>1–9–6–0</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>02/14/2022</t>
+          <t>02/25/2022</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4–5–4–8</t>
+          <t>1–4–3–8</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>02/12/2022</t>
+          <t>02/24/2022</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>8–6–7–6</t>
+          <t>5–7–1–0</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>02/11/2022</t>
+          <t>02/23/2022</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0–1–3–0</t>
+          <t>8–3–8–2</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>02/10/2022</t>
+          <t>02/22/2022</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>7–3–7–4</t>
+          <t>6–0–5–1</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>02/21/2022</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>9–7–1–8</t>
+          <t>8–4–1–4</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>02/08/2022</t>
+          <t>02/19/2022</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>8–7–3–6</t>
+          <t>2–8–5–2</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>02/07/2022</t>
+          <t>02/18/2022</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2–4–4–3</t>
+          <t>4–5–1–7</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>02/05/2022</t>
+          <t>02/17/2022</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>6–4–1–0</t>
+          <t>1–7–3–8</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>02/04/2022</t>
+          <t>02/16/2022</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1–0–9–7</t>
+          <t>2–5–3–1</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>02/03/2022</t>
+          <t>02/15/2022</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8–4–3–0</t>
+          <t>1–1–4–7</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>02/02/2022</t>
+          <t>02/14/2022</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3–0–9–4</t>
+          <t>4–5–4–8</t>
         </is>
       </c>
     </row>
@@ -1931,12 +1931,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>02/01/2022</t>
+          <t>02/12/2022</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>4–0–0–7</t>
+          <t>8–6–7–6</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01/31/2022</t>
+          <t>02/11/2022</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1–9–3–5</t>
+          <t>0–1–3–0</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01/29/2022</t>
+          <t>02/10/2022</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>6–9–0–0</t>
+          <t>7–3–7–4</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01/28/2022</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>5–2–9–3</t>
+          <t>9–7–1–8</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1991,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01/27/2022</t>
+          <t>02/08/2022</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7–4–9–7</t>
+          <t>8–7–3–6</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01/26/2022</t>
+          <t>02/07/2022</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3–8–5–4</t>
+          <t>2–4–4–3</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01/25/2022</t>
+          <t>02/05/2022</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>4–5–7–6</t>
+          <t>6–4–1–0</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01/24/2022</t>
+          <t>02/04/2022</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0–4–7–7</t>
+          <t>1–0–9–7</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01/22/2022</t>
+          <t>02/03/2022</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1–7–1–8</t>
+          <t>8–4–3–0</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01/21/2022</t>
+          <t>02/02/2022</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2–2–8–4</t>
+          <t>3–0–9–4</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>01/20/2022</t>
+          <t>02/01/2022</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>9–6–6–3</t>
+          <t>4–0–0–7</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01/19/2022</t>
+          <t>01/31/2022</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1–1–9–5</t>
+          <t>1–9–3–5</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01/18/2022</t>
+          <t>01/29/2022</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>5–0–2–7</t>
+          <t>6–9–0–0</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01/17/2022</t>
+          <t>01/28/2022</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>5–6–5–6</t>
+          <t>5–2–9–3</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01/15/2022</t>
+          <t>01/27/2022</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>6–8–6–5</t>
+          <t>7–4–9–7</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01/14/2022</t>
+          <t>01/26/2022</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>5–7–4–6</t>
+          <t>3–8–5–4</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01/13/2022</t>
+          <t>01/25/2022</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>6–1–6–2</t>
+          <t>4–5–7–6</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01/12/2022</t>
+          <t>01/24/2022</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>8–5–9–3</t>
+          <t>0–4–7–7</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01/11/2022</t>
+          <t>01/22/2022</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>6–8–6–9</t>
+          <t>1–7–1–8</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/21/2022</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>9–3–7–2</t>
+          <t>2–2–8–4</t>
         </is>
       </c>
     </row>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01/08/2022</t>
+          <t>01/20/2022</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>4–7–3–7</t>
+          <t>9–6–6–3</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/19/2022</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2–4–6–5</t>
+          <t>1–1–9–5</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01/06/2022</t>
+          <t>01/18/2022</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>8–9–3–2</t>
+          <t>5–0–2–7</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01/05/2022</t>
+          <t>01/17/2022</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>7–0–7–3</t>
+          <t>5–6–5–6</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/15/2022</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>9–4–8–7</t>
+          <t>6–8–6–5</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01/03/2022</t>
+          <t>01/14/2022</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>8–1–2–2</t>
+          <t>5–7–4–6</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/13/2022</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>8–0–7–2</t>
+          <t>6–1–6–2</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>01/12/2022</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>4–2–6–5</t>
+          <t>8–5–9–3</t>
         </is>
       </c>
     </row>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>12/30/2021</t>
+          <t>01/11/2022</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2–8–4–6</t>
+          <t>6–8–6–9</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12/29/2021</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2–6–9–0</t>
+          <t>9–3–7–2</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>12/28/2021</t>
+          <t>01/08/2022</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>9–2–6–9</t>
+          <t>4–7–3–7</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>12/27/2021</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>9–6–3–7</t>
+          <t>2–4–6–5</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>12/25/2021</t>
+          <t>01/06/2022</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1–3–6–7</t>
+          <t>8–9–3–2</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>12/24/2021</t>
+          <t>01/05/2022</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>7–9–3–6</t>
+          <t>7–0–7–3</t>
         </is>
       </c>
     </row>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>12/23/2021</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>5–8–8–1</t>
+          <t>9–4–8–7</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>12/22/2021</t>
+          <t>01/03/2022</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>7–1–5–6</t>
+          <t>8–1–2–2</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>12/21/2021</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>5–4–4–9</t>
+          <t>8–0–7–2</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>12/20/2021</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>6–4–7–8</t>
+          <t>4–2–6–5</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>12/18/2021</t>
+          <t>12/30/2021</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>7–7–1–3</t>
+          <t>2–8–4–6</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>12/17/2021</t>
+          <t>12/29/2021</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1–8–8–2</t>
+          <t>2–6–9–0</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>12/16/2021</t>
+          <t>12/28/2021</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>5–4–0–6</t>
+          <t>9–2–6–9</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>12/15/2021</t>
+          <t>12/27/2021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>0–1–4–9</t>
+          <t>9–6–3–7</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>12/14/2021</t>
+          <t>12/25/2021</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>4–7–7–2</t>
+          <t>1–3–6–7</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>12/13/2021</t>
+          <t>12/24/2021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>9–3–8–3</t>
+          <t>7–9–3–6</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2591,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>12/11/2021</t>
+          <t>12/23/2021</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>5–3–3–8</t>
+          <t>5–8–8–1</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>12/10/2021</t>
+          <t>12/22/2021</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>8–3–2–4</t>
+          <t>7–1–5–6</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>12/09/2021</t>
+          <t>12/21/2021</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2–6–0–3</t>
+          <t>5–4–4–9</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>12/20/2021</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>6–3–4–4</t>
+          <t>6–4–7–8</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>12/18/2021</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1–0–0–9</t>
+          <t>7–7–1–3</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>12/06/2021</t>
+          <t>12/17/2021</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>4–5–3–9</t>
+          <t>1–8–8–2</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>12/04/2021</t>
+          <t>12/16/2021</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2–5–6–0</t>
+          <t>5–4–0–6</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>12/03/2021</t>
+          <t>12/15/2021</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>6–8–8–4</t>
+          <t>0–1–4–9</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>12/02/2021</t>
+          <t>12/14/2021</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>8–2–9–5</t>
+          <t>4–7–7–2</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>12/01/2021</t>
+          <t>12/13/2021</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>5–5–9–9</t>
+          <t>9–3–8–3</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>11/30/2021</t>
+          <t>12/11/2021</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>6–9–4–7</t>
+          <t>5–3–3–8</t>
         </is>
       </c>
     </row>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>11/29/2021</t>
+          <t>12/10/2021</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>8–0–3–1</t>
+          <t>8–3–2–4</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>11/27/2021</t>
+          <t>12/09/2021</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>8–1–5–3</t>
+          <t>2–6–0–3</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>11/26/2021</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>8–2–7–2</t>
+          <t>6–3–4–4</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>11/25/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>1–2–0–5</t>
+          <t>1–0–0–9</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>11/24/2021</t>
+          <t>12/06/2021</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>4–3–9–3</t>
+          <t>4–5–3–9</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>11/23/2021</t>
+          <t>12/04/2021</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>4–8–1–1</t>
+          <t>2–5–6–0</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2846,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>11/22/2021</t>
+          <t>12/03/2021</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0–8–0–5</t>
+          <t>6–8–8–4</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>11/20/2021</t>
+          <t>12/02/2021</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>1–9–4–3</t>
+          <t>8–2–9–5</t>
         </is>
       </c>
     </row>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>11/19/2021</t>
+          <t>12/01/2021</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5–3–4–6</t>
+          <t>5–5–9–9</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>11/18/2021</t>
+          <t>11/30/2021</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2–1–0–5</t>
+          <t>6–9–4–7</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>11/17/2021</t>
+          <t>11/29/2021</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>8–8–6–5</t>
+          <t>8–0–3–1</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>11/16/2021</t>
+          <t>11/27/2021</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>7–0–7–3</t>
+          <t>8–1–5–3</t>
         </is>
       </c>
     </row>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>11/15/2021</t>
+          <t>11/26/2021</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>6–8–2–4</t>
+          <t>8–2–7–2</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>11/13/2021</t>
+          <t>11/25/2021</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>6–2–5–8</t>
+          <t>1–2–0–5</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>11/12/2021</t>
+          <t>11/24/2021</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1–5–5–6</t>
+          <t>4–3–9–3</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>11/11/2021</t>
+          <t>11/23/2021</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0–9–9–0</t>
+          <t>4–8–1–1</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>11/10/2021</t>
+          <t>11/22/2021</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>4–5–1–2</t>
+          <t>0–8–0–5</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>11/09/2021</t>
+          <t>11/20/2021</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>6–3–9–5</t>
+          <t>1–9–4–3</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>11/08/2021</t>
+          <t>11/19/2021</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0–6–4–1</t>
+          <t>5–3–4–6</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>11/06/2021</t>
+          <t>11/18/2021</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9–4–6–1</t>
+          <t>2–1–0–5</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>11/05/2021</t>
+          <t>11/17/2021</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>4–6–5–2</t>
+          <t>8–8–6–5</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>11/04/2021</t>
+          <t>11/16/2021</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>9–6–4–5</t>
+          <t>7–0–7–3</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>11/15/2021</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1–2–2–7</t>
+          <t>6–8–2–4</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>11/02/2021</t>
+          <t>11/13/2021</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>4–0–7–2</t>
+          <t>6–2–5–8</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>11/01/2021</t>
+          <t>11/12/2021</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>7–1–0–8</t>
+          <t>1–5–5–6</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>10/30/2021</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>8–2–0–5</t>
+          <t>0–9–9–0</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>10/29/2021</t>
+          <t>11/10/2021</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>5–5–3–5</t>
+          <t>4–5–1–2</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>10/28/2021</t>
+          <t>11/09/2021</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>6–5–9–9</t>
+          <t>6–3–9–5</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>10/27/2021</t>
+          <t>11/08/2021</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>5–7–3–3</t>
+          <t>0–6–4–1</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>10/26/2021</t>
+          <t>11/06/2021</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3–5–3–3</t>
+          <t>9–4–6–1</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>10/25/2021</t>
+          <t>11/05/2021</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>5–3–8–4</t>
+          <t>4–6–5–2</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>10/23/2021</t>
+          <t>11/04/2021</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>4–1–3–4</t>
+          <t>9–6–4–5</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>10/22/2021</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0–5–5–2</t>
+          <t>1–2–2–7</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>10/21/2021</t>
+          <t>11/02/2021</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>1–5–2–2</t>
+          <t>4–0–7–2</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>10/20/2021</t>
+          <t>11/01/2021</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>1–8–9–5</t>
+          <t>7–1–0–8</t>
         </is>
       </c>
     </row>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>10/19/2021</t>
+          <t>10/30/2021</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>6–7–3–8</t>
+          <t>8–2–0–5</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>10/18/2021</t>
+          <t>10/29/2021</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>5–4–3–2</t>
+          <t>5–5–3–5</t>
         </is>
       </c>
     </row>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>10/16/2021</t>
+          <t>10/28/2021</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>5–3–2–8</t>
+          <t>6–5–9–9</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>10/15/2021</t>
+          <t>10/27/2021</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>6–7–3–5</t>
+          <t>5–7–3–3</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>10/14/2021</t>
+          <t>10/26/2021</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>0–8–5–5</t>
+          <t>3–5–3–3</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>10/13/2021</t>
+          <t>10/25/2021</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>0–4–9–6</t>
+          <t>5–3–8–4</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>10/12/2021</t>
+          <t>10/23/2021</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>5–0–4–5</t>
+          <t>4–1–3–4</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>10/11/2021</t>
+          <t>10/22/2021</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>6–7–3–5</t>
+          <t>0–5–5–2</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>10/09/2021</t>
+          <t>10/21/2021</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>0–2–8–4</t>
+          <t>1–5–2–2</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>10/08/2021</t>
+          <t>10/20/2021</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>6–9–3–7</t>
+          <t>1–8–9–5</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>10/07/2021</t>
+          <t>10/19/2021</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>4–8–8–5</t>
+          <t>6–7–3–8</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>10/18/2021</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>6–5–3–8</t>
+          <t>5–4–3–2</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>10/05/2021</t>
+          <t>10/16/2021</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0–3–3–1</t>
+          <t>5–3–2–8</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>10/04/2021</t>
+          <t>10/15/2021</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2–7–7–5</t>
+          <t>6–7–3–5</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>10/02/2021</t>
+          <t>10/14/2021</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>8–7–8–6</t>
+          <t>0–8–5–5</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>10/13/2021</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>9–7–2–2</t>
+          <t>0–4–9–6</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>09/30/2021</t>
+          <t>10/12/2021</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>7–3–7–2</t>
+          <t>5–0–4–5</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>09/29/2021</t>
+          <t>10/11/2021</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>9–5–3–5</t>
+          <t>6–7–3–5</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>09/28/2021</t>
+          <t>10/09/2021</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>5–1–8–5</t>
+          <t>0–2–8–4</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>10/08/2021</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>6–7–6–9</t>
+          <t>6–9–3–7</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>09/25/2021</t>
+          <t>10/07/2021</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>8–1–4–5</t>
+          <t>4–8–8–5</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>09/24/2021</t>
+          <t>10/06/2021</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>3–3–8–6</t>
+          <t>6–5–3–8</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>09/23/2021</t>
+          <t>10/05/2021</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>9–9–1–1</t>
+          <t>0–3–3–1</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>09/22/2021</t>
+          <t>10/04/2021</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>5–7–6–8</t>
+          <t>2–7–7–5</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3641,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>09/21/2021</t>
+          <t>10/02/2021</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>3–6–6–4</t>
+          <t>8–7–8–6</t>
         </is>
       </c>
     </row>
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>10/01/2021</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>1–9–4–4</t>
+          <t>9–7–2–2</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>09/18/2021</t>
+          <t>09/30/2021</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2–3–8–4</t>
+          <t>7–3–7–2</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>09/17/2021</t>
+          <t>09/29/2021</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>7–9–4–3</t>
+          <t>9–5–3–5</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>09/16/2021</t>
+          <t>09/28/2021</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>7–0–6–9</t>
+          <t>5–1–8–5</t>
         </is>
       </c>
     </row>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>09/15/2021</t>
+          <t>09/27/2021</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2–9–0–1</t>
+          <t>6–7–6–9</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>09/14/2021</t>
+          <t>09/25/2021</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>6–8–5–0</t>
+          <t>8–1–4–5</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>09/13/2021</t>
+          <t>09/24/2021</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>7–2–1–3</t>
+          <t>3–3–8–6</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>09/11/2021</t>
+          <t>09/23/2021</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>4–1–2–1</t>
+          <t>9–9–1–1</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3776,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>09/10/2021</t>
+          <t>09/22/2021</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2–3–2–3</t>
+          <t>5–7–6–8</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>09/09/2021</t>
+          <t>09/21/2021</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>0–5–5–4</t>
+          <t>3–6–6–4</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>09/08/2021</t>
+          <t>09/20/2021</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>7–5–5–5</t>
+          <t>1–9–4–4</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>09/18/2021</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>7–8–2–1</t>
+          <t>2–3–8–4</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3836,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>09/06/2021</t>
+          <t>09/17/2021</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>7–2–6–9</t>
+          <t>7–9–4–3</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>09/04/2021</t>
+          <t>09/16/2021</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>7–6–9–3</t>
+          <t>7–0–6–9</t>
         </is>
       </c>
     </row>
@@ -3866,12 +3866,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>09/03/2021</t>
+          <t>09/15/2021</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>7–0–3–4</t>
+          <t>2–9–0–1</t>
         </is>
       </c>
     </row>
@@ -3881,12 +3881,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
+          <t>09/14/2021</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>1–2–1–2</t>
+          <t>6–8–5–0</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>09/01/2021</t>
+          <t>09/13/2021</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>1–7–4–9</t>
+          <t>7–2–1–3</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>08/31/2021</t>
+          <t>09/11/2021</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>8–2–1–4</t>
+          <t>4–1–2–1</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
+          <t>09/10/2021</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>9–7–7–0</t>
+          <t>2–3–2–3</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>08/28/2021</t>
+          <t>09/09/2021</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>3–0–3–3</t>
+          <t>0–5–5–4</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>08/27/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0–1–2–3</t>
+          <t>7–5–5–5</t>
         </is>
       </c>
     </row>
@@ -3971,12 +3971,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>08/26/2021</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>8–5–5–2</t>
+          <t>7–8–2–1</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>08/25/2021</t>
+          <t>09/06/2021</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>5–6–7–8</t>
+          <t>7–2–6–9</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>08/24/2021</t>
+          <t>09/04/2021</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2–4–2–8</t>
+          <t>7–6–9–3</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4016,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>08/23/2021</t>
+          <t>09/03/2021</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>1–6–7–5</t>
+          <t>7–0–3–4</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>08/21/2021</t>
+          <t>09/02/2021</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0–8–0–2</t>
+          <t>1–2–1–2</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>08/20/2021</t>
+          <t>09/01/2021</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>7–9–9–1</t>
+          <t>1–7–4–9</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>08/19/2021</t>
+          <t>08/31/2021</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>8–4–6–8</t>
+          <t>8–2–1–4</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>08/18/2021</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>4–5–0–9</t>
+          <t>9–7–7–0</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>08/17/2021</t>
+          <t>08/28/2021</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>3–2–7–1</t>
+          <t>3–0–3–3</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>08/16/2021</t>
+          <t>08/27/2021</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>8–4–4–8</t>
+          <t>0–1–2–3</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>08/14/2021</t>
+          <t>08/26/2021</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>7–0–3–0</t>
+          <t>8–5–5–2</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>08/13/2021</t>
+          <t>08/25/2021</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>0–7–3–8</t>
+          <t>5–6–7–8</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>08/12/2021</t>
+          <t>08/24/2021</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>3–1–5–2</t>
+          <t>2–4–2–8</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>08/11/2021</t>
+          <t>08/23/2021</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>7–5–9–0</t>
+          <t>1–6–7–5</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>08/10/2021</t>
+          <t>08/21/2021</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>7–2–6–1</t>
+          <t>0–8–0–2</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4196,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>08/09/2021</t>
+          <t>08/20/2021</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>1–1–1–1</t>
+          <t>7–9–9–1</t>
         </is>
       </c>
     </row>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>08/07/2021</t>
+          <t>08/19/2021</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>7–0–0–7</t>
+          <t>8–4–6–8</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>08/18/2021</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>0–2–7–5</t>
+          <t>4–5–0–9</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>08/05/2021</t>
+          <t>08/17/2021</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>5–0–5–3</t>
+          <t>3–2–7–1</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>08/04/2021</t>
+          <t>08/16/2021</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>0–9–2–9</t>
+          <t>8–4–4–8</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>08/03/2021</t>
+          <t>08/14/2021</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>1–2–2–6</t>
+          <t>7–0–3–0</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>08/02/2021</t>
+          <t>08/13/2021</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>5–1–4–0</t>
+          <t>0–7–3–8</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>07/31/2021</t>
+          <t>08/12/2021</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>9–5–8–8</t>
+          <t>3–1–5–2</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>07/30/2021</t>
+          <t>08/11/2021</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>9–6–7–8</t>
+          <t>7–5–9–0</t>
         </is>
       </c>
     </row>
@@ -4331,12 +4331,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>07/29/2021</t>
+          <t>08/10/2021</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>8–1–5–5</t>
+          <t>7–2–6–1</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>07/28/2021</t>
+          <t>08/09/2021</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0–1–3–8</t>
+          <t>1–1–1–1</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>07/27/2021</t>
+          <t>08/07/2021</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>8–7–6–6</t>
+          <t>7–0–0–7</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4376,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>07/26/2021</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>1–2–7–3</t>
+          <t>0–2–7–5</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>07/24/2021</t>
+          <t>08/05/2021</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>8–5–0–4</t>
+          <t>5–0–5–3</t>
         </is>
       </c>
     </row>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>07/23/2021</t>
+          <t>08/04/2021</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>9–8–9–2</t>
+          <t>0–9–2–9</t>
         </is>
       </c>
     </row>
@@ -4421,12 +4421,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>07/22/2021</t>
+          <t>08/03/2021</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>3–4–6–0</t>
+          <t>1–2–2–6</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>07/21/2021</t>
+          <t>08/02/2021</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>9–6–1–6</t>
+          <t>5–1–4–0</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>07/31/2021</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>6–7–1–6</t>
+          <t>9–5–8–8</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>07/19/2021</t>
+          <t>07/30/2021</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>1–6–6–7</t>
+          <t>9–6–7–8</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>07/17/2021</t>
+          <t>07/29/2021</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>6–7–6–5</t>
+          <t>8–1–5–5</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>07/16/2021</t>
+          <t>07/28/2021</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>3–3–0–3</t>
+          <t>0–1–3–8</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>07/15/2021</t>
+          <t>07/27/2021</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>3–2–8–2</t>
+          <t>8–7–6–6</t>
         </is>
       </c>
     </row>
@@ -4526,12 +4526,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>07/14/2021</t>
+          <t>07/26/2021</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>3–4–8–8</t>
+          <t>1–2–7–3</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>07/13/2021</t>
+          <t>07/24/2021</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2–8–6–3</t>
+          <t>8–5–0–4</t>
         </is>
       </c>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>07/12/2021</t>
+          <t>07/23/2021</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>1–7–4–2</t>
+          <t>9–8–9–2</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>07/10/2021</t>
+          <t>07/22/2021</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>6–7–1–2</t>
+          <t>3–4–6–0</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>07/09/2021</t>
+          <t>07/21/2021</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>7–0–5–2</t>
+          <t>9–6–1–6</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>07/08/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>7–8–5–3</t>
+          <t>6–7–1–6</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>07/07/2021</t>
+          <t>07/19/2021</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>1–8–3–3</t>
+          <t>1–6–6–7</t>
         </is>
       </c>
     </row>
@@ -4631,12 +4631,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>07/17/2021</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>9–6–8–2</t>
+          <t>6–7–6–5</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>07/05/2021</t>
+          <t>07/16/2021</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>1–3–3–6</t>
+          <t>3–3–0–3</t>
         </is>
       </c>
     </row>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>07/03/2021</t>
+          <t>07/15/2021</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5–6–1–4</t>
+          <t>3–2–8–2</t>
         </is>
       </c>
     </row>
@@ -4676,12 +4676,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>07/02/2021</t>
+          <t>07/14/2021</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>4–6–8–8</t>
+          <t>3–4–8–8</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>07/01/2021</t>
+          <t>07/13/2021</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>9–5–0–9</t>
+          <t>2–8–6–3</t>
         </is>
       </c>
     </row>
@@ -4706,12 +4706,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>06/30/2021</t>
+          <t>07/12/2021</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>6–0–5–6</t>
+          <t>1–7–4–2</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>07/10/2021</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4–4–8–1</t>
+          <t>6–7–1–2</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>06/28/2021</t>
+          <t>07/09/2021</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>7–7–0–1</t>
+          <t>7–0–5–2</t>
         </is>
       </c>
     </row>
@@ -4751,12 +4751,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>06/26/2021</t>
+          <t>07/08/2021</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>6–1–4–9</t>
+          <t>7–8–5–3</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>06/25/2021</t>
+          <t>07/07/2021</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7–8–8–9</t>
+          <t>1–8–3–3</t>
         </is>
       </c>
     </row>
@@ -4781,12 +4781,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>06/24/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>6–2–4–7</t>
+          <t>9–6–8–2</t>
         </is>
       </c>
     </row>
@@ -4796,12 +4796,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>06/23/2021</t>
+          <t>07/05/2021</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>9–0–6–3</t>
+          <t>1–3–3–6</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>06/22/2021</t>
+          <t>07/03/2021</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>1–6–1–3</t>
+          <t>5–6–1–4</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>06/21/2021</t>
+          <t>07/02/2021</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>1–1–5–9</t>
+          <t>4–6–8–8</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>06/19/2021</t>
+          <t>07/01/2021</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>5–8–3–5</t>
+          <t>9–5–0–9</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4856,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>06/18/2021</t>
+          <t>06/30/2021</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>6–1–0–2</t>
+          <t>6–0–5–6</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4871,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>06/17/2021</t>
+          <t>06/29/2021</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>1–7–3–4</t>
+          <t>4–4–8–1</t>
         </is>
       </c>
     </row>
@@ -4886,12 +4886,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>06/16/2021</t>
+          <t>06/28/2021</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>6–6–5–0</t>
+          <t>7–7–0–1</t>
         </is>
       </c>
     </row>
@@ -4901,12 +4901,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>06/15/2021</t>
+          <t>06/26/2021</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>6–8–8–3</t>
+          <t>6–1–4–9</t>
         </is>
       </c>
     </row>
@@ -4916,12 +4916,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>06/14/2021</t>
+          <t>06/25/2021</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2–7–2–1</t>
+          <t>7–8–8–9</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>06/12/2021</t>
+          <t>06/24/2021</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>7–2–4–6</t>
+          <t>6–2–4–7</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>06/11/2021</t>
+          <t>06/23/2021</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0–3–0–4</t>
+          <t>9–0–6–3</t>
         </is>
       </c>
     </row>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>06/10/2021</t>
+          <t>06/22/2021</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>4–2–8–0</t>
+          <t>1–6–1–3</t>
         </is>
       </c>
     </row>
@@ -4976,12 +4976,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>06/09/2021</t>
+          <t>06/21/2021</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>8–0–4–0</t>
+          <t>1–1–5–9</t>
         </is>
       </c>
     </row>
@@ -4991,12 +4991,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>06/08/2021</t>
+          <t>06/19/2021</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3–9–6–8</t>
+          <t>5–8–3–5</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>06/07/2021</t>
+          <t>06/18/2021</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>5–6–2–5</t>
+          <t>6–1–0–2</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>06/05/2021</t>
+          <t>06/17/2021</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>6–7–7–2</t>
+          <t>1–7–3–4</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
+          <t>06/16/2021</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>6–3–8–1</t>
+          <t>6–6–5–0</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>06/03/2021</t>
+          <t>06/15/2021</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>1–5–8–4</t>
+          <t>6–8–8–3</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>06/02/2021</t>
+          <t>06/14/2021</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>8–1–9–1</t>
+          <t>2–7–2–1</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>06/01/2021</t>
+          <t>06/12/2021</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>9–6–3–0</t>
+          <t>7–2–4–6</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5096,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>05/31/2021</t>
+          <t>06/11/2021</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>1–2–8–3</t>
+          <t>0–3–0–4</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5111,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>05/29/2021</t>
+          <t>06/10/2021</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>5–9–0–4</t>
+          <t>4–2–8–0</t>
         </is>
       </c>
     </row>
@@ -5126,12 +5126,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>05/28/2021</t>
+          <t>06/09/2021</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4–6–0–9</t>
+          <t>8–0–4–0</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>313</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>06/08/2021</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>3–9–6–8</t>
         </is>
       </c>
     </row>

--- a/lottopy_site/lottopy/lottopy_web_edition/daily4.xlsx
+++ b/lottopy_site/lottopy/lottopy_web_edition/daily4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C315"/>
+  <dimension ref="A1:C314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06/08/2022</t>
+          <t>06/10/2022</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7–2–5–5</t>
+          <t>3–8–3–5</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/07/2022</t>
+          <t>06/09/2022</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1–3–3–5</t>
+          <t>6–6–5–9</t>
         </is>
       </c>
     </row>
@@ -476,12 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06/06/2022</t>
+          <t>06/08/2022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1–0–4–2</t>
+          <t>7–2–5–5</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06/04/2022</t>
+          <t>06/07/2022</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5–3–1–8</t>
+          <t>1–3–3–5</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06/03/2022</t>
+          <t>06/06/2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3–6–2–7</t>
+          <t>1–0–4–2</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/02/2022</t>
+          <t>06/04/2022</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2–9–0–1</t>
+          <t>5–3–1–8</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06/01/2022</t>
+          <t>06/03/2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4–2–3–3</t>
+          <t>3–6–2–7</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/31/2022</t>
+          <t>06/02/2022</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4–0–8–3</t>
+          <t>2–9–0–1</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/30/2022</t>
+          <t>06/01/2022</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5–8–1–0</t>
+          <t>4–2–3–3</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/28/2022</t>
+          <t>05/31/2022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4–9–7–6</t>
+          <t>4–0–8–3</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/27/2022</t>
+          <t>05/30/2022</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1–7–9–1</t>
+          <t>5–8–1–0</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05/26/2022</t>
+          <t>05/28/2022</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9–4–5–7</t>
+          <t>4–9–7–6</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/25/2022</t>
+          <t>05/27/2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9–4–2–8</t>
+          <t>1–7–9–1</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/24/2022</t>
+          <t>05/26/2022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1–7–4–5</t>
+          <t>9–4–5–7</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/23/2022</t>
+          <t>05/25/2022</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9–3–1–0</t>
+          <t>9–4–2–8</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/21/2022</t>
+          <t>05/24/2022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8–3–9–6</t>
+          <t>1–7–4–5</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05/20/2022</t>
+          <t>05/23/2022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1–9–4–1</t>
+          <t>9–3–1–0</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05/19/2022</t>
+          <t>05/21/2022</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0–4–9–1</t>
+          <t>8–3–9–6</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>05/18/2022</t>
+          <t>05/20/2022</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4–8–8–3</t>
+          <t>1–9–4–1</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05/17/2022</t>
+          <t>05/19/2022</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7–4–5–0</t>
+          <t>0–4–9–1</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05/16/2022</t>
+          <t>05/18/2022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3–6–4–4</t>
+          <t>4–8–8–3</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05/14/2022</t>
+          <t>05/17/2022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3–3–2–1</t>
+          <t>7–4–5–0</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05/13/2022</t>
+          <t>05/16/2022</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0–6–9–4</t>
+          <t>3–6–4–4</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>05/12/2022</t>
+          <t>05/14/2022</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5–4–2–3</t>
+          <t>3–3–2–1</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>05/11/2022</t>
+          <t>05/13/2022</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9–8–9–8</t>
+          <t>0–6–9–4</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>05/10/2022</t>
+          <t>05/12/2022</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5–7–1–9</t>
+          <t>5–4–2–3</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>05/09/2022</t>
+          <t>05/11/2022</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4–6–1–7</t>
+          <t>9–8–9–8</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>05/07/2022</t>
+          <t>05/10/2022</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7–7–9–9</t>
+          <t>5–7–1–9</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>05/06/2022</t>
+          <t>05/09/2022</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7–9–4–2</t>
+          <t>4–6–1–7</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>05/05/2022</t>
+          <t>05/07/2022</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4–7–6–9</t>
+          <t>7–7–9–9</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>05/04/2022</t>
+          <t>05/06/2022</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3–8–5–3</t>
+          <t>7–9–4–2</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>05/03/2022</t>
+          <t>05/05/2022</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4–2–8–7</t>
+          <t>4–7–6–9</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>05/04/2022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9–9–3–2</t>
+          <t>3–8–5–3</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>04/30/2022</t>
+          <t>05/03/2022</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7–3–1–6</t>
+          <t>4–2–8–7</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>04/29/2022</t>
+          <t>05/02/2022</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6–7–2–0</t>
+          <t>9–9–3–2</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>04/28/2022</t>
+          <t>04/30/2022</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8–8–0–9</t>
+          <t>7–3–1–6</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04/27/2022</t>
+          <t>04/29/2022</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4–9–4–2</t>
+          <t>6–7–2–0</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>04/26/2022</t>
+          <t>04/28/2022</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6–3–0–0</t>
+          <t>8–8–0–9</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>04/25/2022</t>
+          <t>04/27/2022</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0–3–3–5</t>
+          <t>4–9–4–2</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>04/23/2022</t>
+          <t>04/26/2022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4–2–7–9</t>
+          <t>6–3–0–0</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>04/22/2022</t>
+          <t>04/25/2022</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7–4–4–0</t>
+          <t>0–3–3–5</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>04/21/2022</t>
+          <t>04/23/2022</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>8–7–7–5</t>
+          <t>4–2–7–9</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>04/20/2022</t>
+          <t>04/22/2022</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5–6–2–8</t>
+          <t>7–4–4–0</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04/19/2022</t>
+          <t>04/21/2022</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5–6–9–6</t>
+          <t>8–7–7–5</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>04/18/2022</t>
+          <t>04/20/2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0–5–7–7</t>
+          <t>5–6–2–8</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>04/16/2022</t>
+          <t>04/19/2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5–8–5–3</t>
+          <t>5–6–9–6</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>04/15/2022</t>
+          <t>04/18/2022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0–6–8–2</t>
+          <t>0–5–7–7</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>04/14/2022</t>
+          <t>04/16/2022</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8–2–9–7</t>
+          <t>5–8–5–3</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>04/13/2022</t>
+          <t>04/15/2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>7–4–3–7</t>
+          <t>0–6–8–2</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>04/12/2022</t>
+          <t>04/14/2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3–8–9–3</t>
+          <t>8–2–9–7</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>04/11/2022</t>
+          <t>04/13/2022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2–7–8–0</t>
+          <t>7–4–3–7</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>04/09/2022</t>
+          <t>04/12/2022</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9–5–2–7</t>
+          <t>3–8–9–3</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>04/08/2022</t>
+          <t>04/11/2022</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>7–5–1–7</t>
+          <t>2–7–8–0</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>04/07/2022</t>
+          <t>04/09/2022</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4–0–8–8</t>
+          <t>9–5–2–7</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>04/06/2022</t>
+          <t>04/08/2022</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3–3–4–7</t>
+          <t>7–5–1–7</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>04/05/2022</t>
+          <t>04/07/2022</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9–1–9–2</t>
+          <t>4–0–8–8</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>04/04/2022</t>
+          <t>04/06/2022</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>6–9–0–3</t>
+          <t>3–3–4–7</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>04/02/2022</t>
+          <t>04/05/2022</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>4–3–6–2</t>
+          <t>9–1–9–2</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>04/01/2022</t>
+          <t>04/04/2022</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>9–6–0–8</t>
+          <t>6–9–0–3</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>03/31/2022</t>
+          <t>04/02/2022</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>7–9–5–1</t>
+          <t>4–3–6–2</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>03/30/2022</t>
+          <t>04/01/2022</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>6–8–0–2</t>
+          <t>9–6–0–8</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>03/29/2022</t>
+          <t>03/31/2022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8–0–5–6</t>
+          <t>7–9–5–1</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>03/28/2022</t>
+          <t>03/30/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3–8–7–8</t>
+          <t>6–8–0–2</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>03/26/2022</t>
+          <t>03/29/2022</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9–2–6–2</t>
+          <t>8–0–5–6</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>03/25/2022</t>
+          <t>03/28/2022</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0–0–2–7</t>
+          <t>3–8–7–8</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>03/24/2022</t>
+          <t>03/26/2022</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4–9–3–5</t>
+          <t>9–2–6–2</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>03/23/2022</t>
+          <t>03/25/2022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2–0–8–8</t>
+          <t>0–0–2–7</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>03/22/2022</t>
+          <t>03/24/2022</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>5–6–6–6</t>
+          <t>4–9–3–5</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>03/21/2022</t>
+          <t>03/23/2022</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9–5–5–2</t>
+          <t>2–0–8–8</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>03/19/2022</t>
+          <t>03/22/2022</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1–1–4–0</t>
+          <t>5–6–6–6</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>03/18/2022</t>
+          <t>03/21/2022</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>4–0–0–3</t>
+          <t>9–5–5–2</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>03/17/2022</t>
+          <t>03/19/2022</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0–5–5–2</t>
+          <t>1–1–4–0</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>03/16/2022</t>
+          <t>03/18/2022</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1–7–7–4</t>
+          <t>4–0–0–3</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>03/15/2022</t>
+          <t>03/17/2022</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0–9–4–9</t>
+          <t>0–5–5–2</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>03/14/2022</t>
+          <t>03/16/2022</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5–8–8–6</t>
+          <t>1–7–7–4</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>03/12/2022</t>
+          <t>03/15/2022</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>6–2–9–5</t>
+          <t>0–9–4–9</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>03/11/2022</t>
+          <t>03/14/2022</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>8–3–9–0</t>
+          <t>5–8–8–6</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>03/10/2022</t>
+          <t>03/12/2022</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1–8–4–6</t>
+          <t>6–2–9–5</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>03/09/2022</t>
+          <t>03/11/2022</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>4–8–9–1</t>
+          <t>8–3–9–0</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>03/08/2022</t>
+          <t>03/10/2022</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1–8–6–2</t>
+          <t>1–8–4–6</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>03/07/2022</t>
+          <t>03/09/2022</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2–1–0–3</t>
+          <t>4–8–9–1</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>03/08/2022</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>8–2–5–0</t>
+          <t>1–8–6–2</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>03/04/2022</t>
+          <t>03/07/2022</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9–6–5–6</t>
+          <t>2–1–0–3</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>03/03/2022</t>
+          <t>03/05/2022</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3–6–5–5</t>
+          <t>8–2–5–0</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>03/02/2022</t>
+          <t>03/04/2022</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>8–6–1–3</t>
+          <t>9–6–5–6</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>03/01/2022</t>
+          <t>03/03/2022</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0–3–0–4</t>
+          <t>3–6–5–5</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>02/28/2022</t>
+          <t>03/02/2022</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2–1–2–7</t>
+          <t>8–6–1–3</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>02/26/2022</t>
+          <t>03/01/2022</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1–9–6–0</t>
+          <t>0–3–0–4</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>02/25/2022</t>
+          <t>02/28/2022</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1–4–3–8</t>
+          <t>2–1–2–7</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>02/24/2022</t>
+          <t>02/26/2022</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>5–7–1–0</t>
+          <t>1–9–6–0</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>02/23/2022</t>
+          <t>02/25/2022</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>8–3–8–2</t>
+          <t>1–4–3–8</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>02/22/2022</t>
+          <t>02/24/2022</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>6–0–5–1</t>
+          <t>5–7–1–0</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>02/21/2022</t>
+          <t>02/23/2022</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>8–4–1–4</t>
+          <t>8–3–8–2</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>02/19/2022</t>
+          <t>02/22/2022</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2–8–5–2</t>
+          <t>6–0–5–1</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>02/18/2022</t>
+          <t>02/21/2022</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4–5–1–7</t>
+          <t>8–4–1–4</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>02/17/2022</t>
+          <t>02/19/2022</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1–7–3–8</t>
+          <t>2–8–5–2</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>02/16/2022</t>
+          <t>02/18/2022</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2–5–3–1</t>
+          <t>4–5–1–7</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>02/15/2022</t>
+          <t>02/17/2022</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1–1–4–7</t>
+          <t>1–7–3–8</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>02/14/2022</t>
+          <t>02/16/2022</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>4–5–4–8</t>
+          <t>2–5–3–1</t>
         </is>
       </c>
     </row>
@@ -1931,12 +1931,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>02/12/2022</t>
+          <t>02/15/2022</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>8–6–7–6</t>
+          <t>1–1–4–7</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>02/11/2022</t>
+          <t>02/14/2022</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0–1–3–0</t>
+          <t>4–5–4–8</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>02/10/2022</t>
+          <t>02/12/2022</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7–3–7–4</t>
+          <t>8–6–7–6</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>02/11/2022</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>9–7–1–8</t>
+          <t>0–1–3–0</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1991,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>02/08/2022</t>
+          <t>02/10/2022</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>8–7–3–6</t>
+          <t>7–3–7–4</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>02/07/2022</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2–4–4–3</t>
+          <t>9–7–1–8</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>02/05/2022</t>
+          <t>02/08/2022</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>6–4–1–0</t>
+          <t>8–7–3–6</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>02/04/2022</t>
+          <t>02/07/2022</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1–0–9–7</t>
+          <t>2–4–4–3</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>02/03/2022</t>
+          <t>02/05/2022</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>8–4–3–0</t>
+          <t>6–4–1–0</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>02/02/2022</t>
+          <t>02/04/2022</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3–0–9–4</t>
+          <t>1–0–9–7</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>02/01/2022</t>
+          <t>02/03/2022</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4–0–0–7</t>
+          <t>8–4–3–0</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01/31/2022</t>
+          <t>02/02/2022</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1–9–3–5</t>
+          <t>3–0–9–4</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>01/29/2022</t>
+          <t>02/01/2022</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>6–9–0–0</t>
+          <t>4–0–0–7</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>01/28/2022</t>
+          <t>01/31/2022</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>5–2–9–3</t>
+          <t>1–9–3–5</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>01/27/2022</t>
+          <t>01/29/2022</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>7–4–9–7</t>
+          <t>6–9–0–0</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>01/26/2022</t>
+          <t>01/28/2022</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3–8–5–4</t>
+          <t>5–2–9–3</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>01/25/2022</t>
+          <t>01/27/2022</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>4–5–7–6</t>
+          <t>7–4–9–7</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01/24/2022</t>
+          <t>01/26/2022</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>0–4–7–7</t>
+          <t>3–8–5–4</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>01/22/2022</t>
+          <t>01/25/2022</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1–7–1–8</t>
+          <t>4–5–7–6</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01/21/2022</t>
+          <t>01/24/2022</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2–2–8–4</t>
+          <t>0–4–7–7</t>
         </is>
       </c>
     </row>
@@ -2231,12 +2231,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01/20/2022</t>
+          <t>01/22/2022</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>9–6–6–3</t>
+          <t>1–7–1–8</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01/19/2022</t>
+          <t>01/21/2022</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1–1–9–5</t>
+          <t>2–2–8–4</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01/18/2022</t>
+          <t>01/20/2022</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>5–0–2–7</t>
+          <t>9–6–6–3</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01/17/2022</t>
+          <t>01/19/2022</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>5–6–5–6</t>
+          <t>1–1–9–5</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01/15/2022</t>
+          <t>01/18/2022</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>6–8–6–5</t>
+          <t>5–0–2–7</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01/14/2022</t>
+          <t>01/17/2022</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>5–7–4–6</t>
+          <t>5–6–5–6</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01/13/2022</t>
+          <t>01/15/2022</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>6–1–6–2</t>
+          <t>6–8–6–5</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01/12/2022</t>
+          <t>01/14/2022</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>8–5–9–3</t>
+          <t>5–7–4–6</t>
         </is>
       </c>
     </row>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01/11/2022</t>
+          <t>01/13/2022</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>6–8–6–9</t>
+          <t>6–1–6–2</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/12/2022</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>9–3–7–2</t>
+          <t>8–5–9–3</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01/08/2022</t>
+          <t>01/11/2022</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>4–7–3–7</t>
+          <t>6–8–6–9</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01/07/2022</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2–4–6–5</t>
+          <t>9–3–7–2</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01/06/2022</t>
+          <t>01/08/2022</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>8–9–3–2</t>
+          <t>4–7–3–7</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01/05/2022</t>
+          <t>01/07/2022</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>7–0–7–3</t>
+          <t>2–4–6–5</t>
         </is>
       </c>
     </row>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/06/2022</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>9–4–8–7</t>
+          <t>8–9–3–2</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2456,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01/03/2022</t>
+          <t>01/05/2022</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>8–1–2–2</t>
+          <t>7–0–7–3</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>8–0–7–2</t>
+          <t>9–4–8–7</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>12/31/2021</t>
+          <t>01/03/2022</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>4–2–6–5</t>
+          <t>8–1–2–2</t>
         </is>
       </c>
     </row>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>12/30/2021</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2–8–4–6</t>
+          <t>8–0–7–2</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>12/29/2021</t>
+          <t>12/31/2021</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2–6–9–0</t>
+          <t>4–2–6–5</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>12/28/2021</t>
+          <t>12/30/2021</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>9–2–6–9</t>
+          <t>2–8–4–6</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>12/27/2021</t>
+          <t>12/29/2021</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>9–6–3–7</t>
+          <t>2–6–9–0</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>12/25/2021</t>
+          <t>12/28/2021</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1–3–6–7</t>
+          <t>9–2–6–9</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>12/24/2021</t>
+          <t>12/27/2021</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7–9–3–6</t>
+          <t>9–6–3–7</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2591,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>12/23/2021</t>
+          <t>12/25/2021</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>5–8–8–1</t>
+          <t>1–3–6–7</t>
         </is>
       </c>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>12/22/2021</t>
+          <t>12/24/2021</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7–1–5–6</t>
+          <t>7–9–3–6</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>12/21/2021</t>
+          <t>12/23/2021</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>5–4–4–9</t>
+          <t>5–8–8–1</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>12/20/2021</t>
+          <t>12/22/2021</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>6–4–7–8</t>
+          <t>7–1–5–6</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>12/18/2021</t>
+          <t>12/21/2021</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>7–7–1–3</t>
+          <t>5–4–4–9</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>12/17/2021</t>
+          <t>12/20/2021</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>1–8–8–2</t>
+          <t>6–4–7–8</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>12/16/2021</t>
+          <t>12/18/2021</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>5–4–0–6</t>
+          <t>7–7–1–3</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>12/15/2021</t>
+          <t>12/17/2021</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0–1–4–9</t>
+          <t>1–8–8–2</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2711,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>12/14/2021</t>
+          <t>12/16/2021</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>4–7–7–2</t>
+          <t>5–4–0–6</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>12/13/2021</t>
+          <t>12/15/2021</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>9–3–8–3</t>
+          <t>0–1–4–9</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>12/11/2021</t>
+          <t>12/14/2021</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>5–3–3–8</t>
+          <t>4–7–7–2</t>
         </is>
       </c>
     </row>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>12/10/2021</t>
+          <t>12/13/2021</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>8–3–2–4</t>
+          <t>9–3–8–3</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>12/09/2021</t>
+          <t>12/11/2021</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2–6–0–3</t>
+          <t>5–3–3–8</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>12/08/2021</t>
+          <t>12/10/2021</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>6–3–4–4</t>
+          <t>8–3–2–4</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>12/07/2021</t>
+          <t>12/09/2021</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>1–0–0–9</t>
+          <t>2–6–0–3</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>12/06/2021</t>
+          <t>12/08/2021</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>4–5–3–9</t>
+          <t>6–3–4–4</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>12/04/2021</t>
+          <t>12/07/2021</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2–5–6–0</t>
+          <t>1–0–0–9</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2846,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>12/03/2021</t>
+          <t>12/06/2021</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>6–8–8–4</t>
+          <t>4–5–3–9</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>12/02/2021</t>
+          <t>12/04/2021</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>8–2–9–5</t>
+          <t>2–5–6–0</t>
         </is>
       </c>
     </row>
@@ -2876,12 +2876,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>12/01/2021</t>
+          <t>12/03/2021</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5–5–9–9</t>
+          <t>6–8–8–4</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>11/30/2021</t>
+          <t>12/02/2021</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>6–9–4–7</t>
+          <t>8–2–9–5</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>11/29/2021</t>
+          <t>12/01/2021</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>8–0–3–1</t>
+          <t>5–5–9–9</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>11/27/2021</t>
+          <t>11/30/2021</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>8–1–5–3</t>
+          <t>6–9–4–7</t>
         </is>
       </c>
     </row>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>11/26/2021</t>
+          <t>11/29/2021</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>8–2–7–2</t>
+          <t>8–0–3–1</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>11/25/2021</t>
+          <t>11/27/2021</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>1–2–0–5</t>
+          <t>8–1–5–3</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>11/24/2021</t>
+          <t>11/26/2021</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>4–3–9–3</t>
+          <t>8–2–7–2</t>
         </is>
       </c>
     </row>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>11/23/2021</t>
+          <t>11/25/2021</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>4–8–1–1</t>
+          <t>1–2–0–5</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>11/22/2021</t>
+          <t>11/24/2021</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0–8–0–5</t>
+          <t>4–3–9–3</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>11/20/2021</t>
+          <t>11/23/2021</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1–9–4–3</t>
+          <t>4–8–1–1</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>11/19/2021</t>
+          <t>11/22/2021</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>5–3–4–6</t>
+          <t>0–8–0–5</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>11/18/2021</t>
+          <t>11/20/2021</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2–1–0–5</t>
+          <t>1–9–4–3</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>11/17/2021</t>
+          <t>11/19/2021</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>8–8–6–5</t>
+          <t>5–3–4–6</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>11/16/2021</t>
+          <t>11/18/2021</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>7–0–7–3</t>
+          <t>2–1–0–5</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>11/15/2021</t>
+          <t>11/17/2021</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>6–8–2–4</t>
+          <t>8–8–6–5</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>11/13/2021</t>
+          <t>11/16/2021</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>6–2–5–8</t>
+          <t>7–0–7–3</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>11/12/2021</t>
+          <t>11/15/2021</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1–5–5–6</t>
+          <t>6–8–2–4</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>11/11/2021</t>
+          <t>11/13/2021</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0–9–9–0</t>
+          <t>6–2–5–8</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>11/10/2021</t>
+          <t>11/12/2021</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>4–5–1–2</t>
+          <t>1–5–5–6</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>11/09/2021</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>6–3–9–5</t>
+          <t>0–9–9–0</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3176,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>11/08/2021</t>
+          <t>11/10/2021</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0–6–4–1</t>
+          <t>4–5–1–2</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>11/06/2021</t>
+          <t>11/09/2021</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>9–4–6–1</t>
+          <t>6–3–9–5</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>11/05/2021</t>
+          <t>11/08/2021</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>4–6–5–2</t>
+          <t>0–6–4–1</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>11/04/2021</t>
+          <t>11/06/2021</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>9–6–4–5</t>
+          <t>9–4–6–1</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>11/03/2021</t>
+          <t>11/05/2021</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>1–2–2–7</t>
+          <t>4–6–5–2</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>11/02/2021</t>
+          <t>11/04/2021</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>4–0–7–2</t>
+          <t>9–6–4–5</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>11/01/2021</t>
+          <t>11/03/2021</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>7–1–0–8</t>
+          <t>1–2–2–7</t>
         </is>
       </c>
     </row>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>10/30/2021</t>
+          <t>11/02/2021</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>8–2–0–5</t>
+          <t>4–0–7–2</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>10/29/2021</t>
+          <t>11/01/2021</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>5–5–3–5</t>
+          <t>7–1–0–8</t>
         </is>
       </c>
     </row>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>10/28/2021</t>
+          <t>10/30/2021</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>6–5–9–9</t>
+          <t>8–2–0–5</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>10/27/2021</t>
+          <t>10/29/2021</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>5–7–3–3</t>
+          <t>5–5–3–5</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>10/26/2021</t>
+          <t>10/28/2021</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>3–5–3–3</t>
+          <t>6–5–9–9</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>10/25/2021</t>
+          <t>10/27/2021</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>5–3–8–4</t>
+          <t>5–7–3–3</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>10/23/2021</t>
+          <t>10/26/2021</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>4–1–3–4</t>
+          <t>3–5–3–3</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>10/22/2021</t>
+          <t>10/25/2021</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>0–5–5–2</t>
+          <t>5–3–8–4</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>10/21/2021</t>
+          <t>10/23/2021</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1–5–2–2</t>
+          <t>4–1–3–4</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>10/20/2021</t>
+          <t>10/22/2021</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>1–8–9–5</t>
+          <t>0–5–5–2</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>10/19/2021</t>
+          <t>10/21/2021</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>6–7–3–8</t>
+          <t>1–5–2–2</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>10/18/2021</t>
+          <t>10/20/2021</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>5–4–3–2</t>
+          <t>1–8–9–5</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>10/16/2021</t>
+          <t>10/19/2021</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>5–3–2–8</t>
+          <t>6–7–3–8</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>10/15/2021</t>
+          <t>10/18/2021</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>6–7–3–5</t>
+          <t>5–4–3–2</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>10/14/2021</t>
+          <t>10/16/2021</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0–8–5–5</t>
+          <t>5–3–2–8</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>10/13/2021</t>
+          <t>10/15/2021</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>0–4–9–6</t>
+          <t>6–7–3–5</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>10/12/2021</t>
+          <t>10/14/2021</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>5–0–4–5</t>
+          <t>0–8–5–5</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>10/11/2021</t>
+          <t>10/13/2021</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>6–7–3–5</t>
+          <t>0–4–9–6</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>10/09/2021</t>
+          <t>10/12/2021</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>0–2–8–4</t>
+          <t>5–0–4–5</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>10/08/2021</t>
+          <t>10/11/2021</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>6–9–3–7</t>
+          <t>6–7–3–5</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>10/07/2021</t>
+          <t>10/09/2021</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>4–8–8–5</t>
+          <t>0–2–8–4</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>10/08/2021</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>6–5–3–8</t>
+          <t>6–9–3–7</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>10/05/2021</t>
+          <t>10/07/2021</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>0–3–3–1</t>
+          <t>4–8–8–5</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>10/04/2021</t>
+          <t>10/06/2021</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2–7–7–5</t>
+          <t>6–5–3–8</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3641,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>10/02/2021</t>
+          <t>10/05/2021</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>8–7–8–6</t>
+          <t>0–3–3–1</t>
         </is>
       </c>
     </row>
@@ -3656,12 +3656,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>10/04/2021</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>9–7–2–2</t>
+          <t>2–7–7–5</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>09/30/2021</t>
+          <t>10/02/2021</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>7–3–7–2</t>
+          <t>8–7–8–6</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>09/29/2021</t>
+          <t>10/01/2021</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>9–5–3–5</t>
+          <t>9–7–2–2</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>09/28/2021</t>
+          <t>09/30/2021</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>5–1–8–5</t>
+          <t>7–3–7–2</t>
         </is>
       </c>
     </row>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>09/27/2021</t>
+          <t>09/29/2021</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>6–7–6–9</t>
+          <t>9–5–3–5</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>09/25/2021</t>
+          <t>09/28/2021</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>8–1–4–5</t>
+          <t>5–1–8–5</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>09/24/2021</t>
+          <t>09/27/2021</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>3–3–8–6</t>
+          <t>6–7–6–9</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>09/23/2021</t>
+          <t>09/25/2021</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>9–9–1–1</t>
+          <t>8–1–4–5</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3776,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>09/22/2021</t>
+          <t>09/24/2021</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>5–7–6–8</t>
+          <t>3–3–8–6</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>09/21/2021</t>
+          <t>09/23/2021</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>3–6–6–4</t>
+          <t>9–9–1–1</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>09/20/2021</t>
+          <t>09/22/2021</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1–9–4–4</t>
+          <t>5–7–6–8</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>09/18/2021</t>
+          <t>09/21/2021</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2–3–8–4</t>
+          <t>3–6–6–4</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3836,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>09/17/2021</t>
+          <t>09/20/2021</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>7–9–4–3</t>
+          <t>1–9–4–4</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>09/16/2021</t>
+          <t>09/18/2021</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>7–0–6–9</t>
+          <t>2–3–8–4</t>
         </is>
       </c>
     </row>
@@ -3866,12 +3866,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>09/15/2021</t>
+          <t>09/17/2021</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2–9–0–1</t>
+          <t>7–9–4–3</t>
         </is>
       </c>
     </row>
@@ -3881,12 +3881,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>09/14/2021</t>
+          <t>09/16/2021</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>6–8–5–0</t>
+          <t>7–0–6–9</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>09/13/2021</t>
+          <t>09/15/2021</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>7–2–1–3</t>
+          <t>2–9–0–1</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>09/11/2021</t>
+          <t>09/14/2021</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>4–1–2–1</t>
+          <t>6–8–5–0</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>09/10/2021</t>
+          <t>09/13/2021</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2–3–2–3</t>
+          <t>7–2–1–3</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>09/09/2021</t>
+          <t>09/11/2021</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0–5–5–4</t>
+          <t>4–1–2–1</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>09/08/2021</t>
+          <t>09/10/2021</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>7–5–5–5</t>
+          <t>2–3–2–3</t>
         </is>
       </c>
     </row>
@@ -3971,12 +3971,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>09/07/2021</t>
+          <t>09/09/2021</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>7–8–2–1</t>
+          <t>0–5–5–4</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>09/06/2021</t>
+          <t>09/08/2021</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>7–2–6–9</t>
+          <t>7–5–5–5</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>09/04/2021</t>
+          <t>09/07/2021</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>7–6–9–3</t>
+          <t>7–8–2–1</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4016,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>09/03/2021</t>
+          <t>09/06/2021</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>7–0–3–4</t>
+          <t>7–2–6–9</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
+          <t>09/04/2021</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>1–2–1–2</t>
+          <t>7–6–9–3</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>09/01/2021</t>
+          <t>09/03/2021</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>1–7–4–9</t>
+          <t>7–0–3–4</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>08/31/2021</t>
+          <t>09/02/2021</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>8–2–1–4</t>
+          <t>1–2–1–2</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
+          <t>09/01/2021</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>9–7–7–0</t>
+          <t>1–7–4–9</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>08/28/2021</t>
+          <t>08/31/2021</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>3–0–3–3</t>
+          <t>8–2–1–4</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>08/27/2021</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>0–1–2–3</t>
+          <t>9–7–7–0</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>08/26/2021</t>
+          <t>08/28/2021</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>8–5–5–2</t>
+          <t>3–0–3–3</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>08/25/2021</t>
+          <t>08/27/2021</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>5–6–7–8</t>
+          <t>0–1–2–3</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>08/24/2021</t>
+          <t>08/26/2021</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2–4–2–8</t>
+          <t>8–5–5–2</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>08/23/2021</t>
+          <t>08/25/2021</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>1–6–7–5</t>
+          <t>5–6–7–8</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>08/21/2021</t>
+          <t>08/24/2021</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>0–8–0–2</t>
+          <t>2–4–2–8</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4196,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>08/20/2021</t>
+          <t>08/23/2021</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>7–9–9–1</t>
+          <t>1–6–7–5</t>
         </is>
       </c>
     </row>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>08/19/2021</t>
+          <t>08/21/2021</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>8–4–6–8</t>
+          <t>0–8–0–2</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>08/18/2021</t>
+          <t>08/20/2021</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4–5–0–9</t>
+          <t>7–9–9–1</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>08/17/2021</t>
+          <t>08/19/2021</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3–2–7–1</t>
+          <t>8–4–6–8</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>08/16/2021</t>
+          <t>08/18/2021</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>8–4–4–8</t>
+          <t>4–5–0–9</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>08/14/2021</t>
+          <t>08/17/2021</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>7–0–3–0</t>
+          <t>3–2–7–1</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>08/13/2021</t>
+          <t>08/16/2021</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>0–7–3–8</t>
+          <t>8–4–4–8</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>08/12/2021</t>
+          <t>08/14/2021</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>3–1–5–2</t>
+          <t>7–0–3–0</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>08/11/2021</t>
+          <t>08/13/2021</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>7–5–9–0</t>
+          <t>0–7–3–8</t>
         </is>
       </c>
     </row>
@@ -4331,12 +4331,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>08/10/2021</t>
+          <t>08/12/2021</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>7–2–6–1</t>
+          <t>3–1–5–2</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>08/09/2021</t>
+          <t>08/11/2021</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>1–1–1–1</t>
+          <t>7–5–9–0</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>08/07/2021</t>
+          <t>08/10/2021</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>7–0–0–7</t>
+          <t>7–2–6–1</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4376,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>08/06/2021</t>
+          <t>08/09/2021</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>0–2–7–5</t>
+          <t>1–1–1–1</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>08/05/2021</t>
+          <t>08/07/2021</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>5–0–5–3</t>
+          <t>7–0–0–7</t>
         </is>
       </c>
     </row>
@@ -4406,12 +4406,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>08/04/2021</t>
+          <t>08/06/2021</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>0–9–2–9</t>
+          <t>0–2–7–5</t>
         </is>
       </c>
     </row>
@@ -4421,12 +4421,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>08/03/2021</t>
+          <t>08/05/2021</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>1–2–2–6</t>
+          <t>5–0–5–3</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>08/02/2021</t>
+          <t>08/04/2021</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>5–1–4–0</t>
+          <t>0–9–2–9</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>07/31/2021</t>
+          <t>08/03/2021</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>9–5–8–8</t>
+          <t>1–2–2–6</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>07/30/2021</t>
+          <t>08/02/2021</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>9–6–7–8</t>
+          <t>5–1–4–0</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>07/29/2021</t>
+          <t>07/31/2021</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>8–1–5–5</t>
+          <t>9–5–8–8</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>07/28/2021</t>
+          <t>07/30/2021</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>0–1–3–8</t>
+          <t>9–6–7–8</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>07/27/2021</t>
+          <t>07/29/2021</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>8–7–6–6</t>
+          <t>8–1–5–5</t>
         </is>
       </c>
     </row>
@@ -4526,12 +4526,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>07/26/2021</t>
+          <t>07/28/2021</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>1–2–7–3</t>
+          <t>0–1–3–8</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>07/24/2021</t>
+          <t>07/27/2021</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>8–5–0–4</t>
+          <t>8–7–6–6</t>
         </is>
       </c>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>07/23/2021</t>
+          <t>07/26/2021</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>9–8–9–2</t>
+          <t>1–2–7–3</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>07/22/2021</t>
+          <t>07/24/2021</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>3–4–6–0</t>
+          <t>8–5–0–4</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>07/21/2021</t>
+          <t>07/23/2021</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>9–6–1–6</t>
+          <t>9–8–9–2</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>07/20/2021</t>
+          <t>07/22/2021</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>6–7–1–6</t>
+          <t>3–4–6–0</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>07/19/2021</t>
+          <t>07/21/2021</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>1–6–6–7</t>
+          <t>9–6–1–6</t>
         </is>
       </c>
     </row>
@@ -4631,12 +4631,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>07/17/2021</t>
+          <t>07/20/2021</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>6–7–6–5</t>
+          <t>6–7–1–6</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>07/16/2021</t>
+          <t>07/19/2021</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>3–3–0–3</t>
+          <t>1–6–6–7</t>
         </is>
       </c>
     </row>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>07/15/2021</t>
+          <t>07/17/2021</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>3–2–8–2</t>
+          <t>6–7–6–5</t>
         </is>
       </c>
     </row>
@@ -4676,12 +4676,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>07/14/2021</t>
+          <t>07/16/2021</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>3–4–8–8</t>
+          <t>3–3–0–3</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>07/13/2021</t>
+          <t>07/15/2021</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2–8–6–3</t>
+          <t>3–2–8–2</t>
         </is>
       </c>
     </row>
@@ -4706,12 +4706,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>07/12/2021</t>
+          <t>07/14/2021</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>1–7–4–2</t>
+          <t>3–4–8–8</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>07/10/2021</t>
+          <t>07/13/2021</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>6–7–1–2</t>
+          <t>2–8–6–3</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>07/09/2021</t>
+          <t>07/12/2021</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>7–0–5–2</t>
+          <t>1–7–4–2</t>
         </is>
       </c>
     </row>
@@ -4751,12 +4751,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>07/08/2021</t>
+          <t>07/10/2021</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>7–8–5–3</t>
+          <t>6–7–1–2</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>07/07/2021</t>
+          <t>07/09/2021</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>1–8–3–3</t>
+          <t>7–0–5–2</t>
         </is>
       </c>
     </row>
@@ -4781,12 +4781,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>07/06/2021</t>
+          <t>07/08/2021</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>9–6–8–2</t>
+          <t>7–8–5–3</t>
         </is>
       </c>
     </row>
@@ -4796,12 +4796,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>07/05/2021</t>
+          <t>07/07/2021</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>1–3–3–6</t>
+          <t>1–8–3–3</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>07/03/2021</t>
+          <t>07/06/2021</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>5–6–1–4</t>
+          <t>9–6–8–2</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>07/02/2021</t>
+          <t>07/05/2021</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>4–6–8–8</t>
+          <t>1–3–3–6</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>07/01/2021</t>
+          <t>07/03/2021</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>9–5–0–9</t>
+          <t>5–6–1–4</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4856,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>06/30/2021</t>
+          <t>07/02/2021</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>6–0–5–6</t>
+          <t>4–6–8–8</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4871,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>06/29/2021</t>
+          <t>07/01/2021</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>4–4–8–1</t>
+          <t>9–5–0–9</t>
         </is>
       </c>
     </row>
@@ -4886,12 +4886,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>06/28/2021</t>
+          <t>06/30/2021</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>7–7–0–1</t>
+          <t>6–0–5–6</t>
         </is>
       </c>
     </row>
@@ -4901,12 +4901,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>06/26/2021</t>
+          <t>06/29/2021</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>6–1–4–9</t>
+          <t>4–4–8–1</t>
         </is>
       </c>
     </row>
@@ -4916,12 +4916,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>06/25/2021</t>
+          <t>06/28/2021</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>7–8–8–9</t>
+          <t>7–7–0–1</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>06/24/2021</t>
+          <t>06/26/2021</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>6–2–4–7</t>
+          <t>6–1–4–9</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>06/23/2021</t>
+          <t>06/25/2021</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>9–0–6–3</t>
+          <t>7–8–8–9</t>
         </is>
       </c>
     </row>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>06/22/2021</t>
+          <t>06/24/2021</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>1–6–1–3</t>
+          <t>6–2–4–7</t>
         </is>
       </c>
     </row>
@@ -4976,12 +4976,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>06/21/2021</t>
+          <t>06/23/2021</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>1–1–5–9</t>
+          <t>9–0–6–3</t>
         </is>
       </c>
     </row>
@@ -4991,12 +4991,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>06/19/2021</t>
+          <t>06/22/2021</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>5–8–3–5</t>
+          <t>1–6–1–3</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>06/18/2021</t>
+          <t>06/21/2021</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>6–1–0–2</t>
+          <t>1–1–5–9</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>06/17/2021</t>
+          <t>06/19/2021</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>1–7–3–4</t>
+          <t>5–8–3–5</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>06/16/2021</t>
+          <t>06/18/2021</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>6–6–5–0</t>
+          <t>6–1–0–2</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>06/15/2021</t>
+          <t>06/17/2021</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>6–8–8–3</t>
+          <t>1–7–3–4</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>06/14/2021</t>
+          <t>06/16/2021</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2–7–2–1</t>
+          <t>6–6–5–0</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>06/12/2021</t>
+          <t>06/15/2021</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>7–2–4–6</t>
+          <t>6–8–8–3</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5096,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>06/11/2021</t>
+          <t>06/14/2021</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>0–3–0–4</t>
+          <t>2–7–2–1</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5111,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>06/10/2021</t>
+          <t>06/12/2021</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>4–2–8–0</t>
+          <t>7–2–4–6</t>
         </is>
       </c>
     </row>
@@ -5126,27 +5126,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>06/09/2021</t>
+          <t>06/11/2021</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>8–0–4–0</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="1" t="n">
-        <v>313</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>06/08/2021</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>3–9–6–8</t>
+          <t>0–3–0–4</t>
         </is>
       </c>
     </row>
